--- a/tame_output/ON/bt/strategyON_20240429.xlsx
+++ b/tame_output/ON/bt/strategyON_20240429.xlsx
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832483278809</v>
+        <v>3.748324832788089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749179</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145934</v>
+        <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009946</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966253</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.79126997604699</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.762643902144509</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978365</v>
+        <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734158</v>
+        <v>3.784340376734154</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212294</v>
+        <v>3.786946382212291</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786042</v>
+        <v>3.752023923786038</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273184</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279493</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.74828224103042</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.400130007456827</v>
+        <v>3.400130007456823</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.489215576074983</v>
+        <v>-4.488951331662167</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9578014616170591</v>
+        <v>0.9579071593821855</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.7034245210155308</v>
+        <v>-0.703160276602715</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.331789403751481</v>
+        <v>2.331947950399171</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240429.xlsx
+++ b/tame_output/ON/bt/strategyON_20240429.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>55.3%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.0%</t>
+          <t>116.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.2%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.6%</t>
+          <t>-58.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.4%</t>
+          <t>444.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-610.5%</t>
+          <t>-595.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-45.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-112.1%</t>
+          <t>-65.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.4%</t>
+          <t>-274.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.8%</t>
+          <t>-169.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-294.3%</t>
+          <t>-285.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-212.8%</t>
+          <t>-207.3%</t>
         </is>
       </c>
     </row>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.45757074175625</v>
+        <v>-12.30201228396238</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.821630545565101</v>
+        <v>-1.75940716244755</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.606166793021496</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9416978208695514</v>
+        <v>0.9980540996382503</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.40555522778744</v>
+        <v>-12.24999676999356</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.796834004291174</v>
+        <v>-1.734610621173625</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.606166793021496</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9456881565559523</v>
+        <v>1.002044435324651</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.54722706951156</v>
+        <v>-12.39166861171768</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.854977967879564</v>
+        <v>-1.792754584762014</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.606166793021496</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9442129296572106</v>
+        <v>1.000569208425909</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.64613380997083</v>
+        <v>-12.49057535217696</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.879487253898402</v>
+        <v>-1.817263870780852</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.799000664761936</v>
+        <v>-3.705073533480772</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8999222955465176</v>
+        <v>0.9562785743152165</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.44698170273374</v>
+        <v>-12.29142324493986</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.812877544650246</v>
+        <v>-1.750654161532696</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.633678138812123</v>
+        <v>-3.539751007530958</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9860646774697228</v>
+        <v>1.042420956238421</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.22113655001433</v>
+        <v>-12.06557809222045</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.712960410526273</v>
+        <v>-1.650737027408722</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.497824331943795</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.02079975585823</v>
+        <v>1.077156034626928</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.93486173769163</v>
+        <v>-11.77930327989775</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.597311341041136</v>
+        <v>-1.535087957923585</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.497824331943795</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.021938900414288</v>
+        <v>1.078295179182987</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.98775702573592</v>
+        <v>-11.83219856794204</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.615835682096743</v>
+        <v>-1.553612298979192</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.492868985855349</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.027545882229464</v>
+        <v>1.083902160998163</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.70384829480717</v>
+        <v>-11.54828983701329</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.496538485486607</v>
+        <v>-1.434315102369056</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.492868985855349</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.0332795864681</v>
+        <v>1.089635865236799</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.58842737066907</v>
+        <v>-11.4328689128752</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.460107378225233</v>
+        <v>-1.397883995107683</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.377448061717253</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.092794878557092</v>
+        <v>1.149151157325791</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.324590503465</v>
+        <v>-11.16903204567113</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.364456112656514</v>
+        <v>-1.302232729538962</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.377448061717253</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.082911397244185</v>
+        <v>1.139267676012884</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-11.0573487025966</v>
+        <v>-10.90179024480273</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.259393952808528</v>
+        <v>-1.197170569690977</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.377448061717253</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.081076836744811</v>
+        <v>1.13743311551351</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.93404277411839</v>
+        <v>-10.77848431632451</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.210371896390701</v>
+        <v>-1.148148513273151</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.381957521870854</v>
+        <v>-3.28803039058969</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.134427124447888</v>
+        <v>1.190783403216587</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.91008923314243</v>
+        <v>-10.75453077534855</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.200121973854824</v>
+        <v>-1.137898590737274</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.358003980894897</v>
+        <v>-3.264076849613732</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.149467755178956</v>
+        <v>1.205824033947655</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.64602929481963</v>
+        <v>-10.49047083702575</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.107758314687458</v>
+        <v>-1.045534931569907</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.000016911290936</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.294643402010882</v>
+        <v>1.350999680779581</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.938949671314793</v>
+        <v>-9.783391213520916</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.8277134989458235</v>
+        <v>-0.765490115828273</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.000016911290936</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.291856368350581</v>
+        <v>1.34821264711928</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.898765372948603</v>
+        <v>-9.743206915154726</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.8112961557115059</v>
+        <v>-0.7490727725939554</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.05375974420591</v>
+        <v>-2.959832612924745</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.316310571258137</v>
+        <v>1.372666850026836</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.818695577410798</v>
+        <v>-9.663137119616922</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7799014162756275</v>
+        <v>-0.7176780331580765</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.973689948668106</v>
+        <v>-2.879762817386941</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.363719269801576</v>
+        <v>1.420075548570275</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.585214355181201</v>
+        <v>-9.429655897387324</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6785844985459359</v>
+        <v>-0.6163611154283855</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.740208726438507</v>
+        <v>-2.646281595157343</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.511732431977188</v>
+        <v>1.568088710745886</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.405505825037327</v>
+        <v>-9.24994736724345</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.6095932968013456</v>
+        <v>-0.5473699136837951</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.683037222275811</v>
+        <v>-2.589110090994647</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.543143124161846</v>
+        <v>1.599499402930545</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.27323035140644</v>
+        <v>-9.117671893612563</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.5613156206019636</v>
+        <v>-0.4990922374844131</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.550761748644925</v>
+        <v>-2.45683461736376</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.617875895087405</v>
+        <v>1.674232173856104</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-9.082630676733286</v>
+        <v>-8.92707221893941</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4822606900450657</v>
+        <v>-0.4200373069275152</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.266234942690608</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.735050760578933</v>
+        <v>1.791407039347632</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.833630878049705</v>
+        <v>-8.678072420255829</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3697544293479744</v>
+        <v>-0.3075310462304239</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.266234942690608</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.747957101802592</v>
+        <v>1.804313380571291</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.93922086782281</v>
+        <v>-8.783662410028933</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5399663548564351</v>
+        <v>-0.4777429717388841</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.371824932463712</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.556627178339511</v>
+        <v>1.612983457108209</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.957955769941407</v>
+        <v>-8.80239731214753</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4989159738267874</v>
+        <v>-0.4366925907092369</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.371824932463712</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.605171520216597</v>
+        <v>1.661527798985296</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.810015728533807</v>
+        <v>-8.654457270739931</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5596188799519153</v>
+        <v>-0.4973954968343648</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.445431147836319</v>
+        <v>-2.351504016555154</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.497485147073564</v>
+        <v>1.553841425842263</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.785787092144835</v>
+        <v>-8.630228634350958</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.5586414116498046</v>
+        <v>-0.4964180285322537</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.327275380166182</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.503308342653469</v>
+        <v>1.559664621422168</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.742238685374144</v>
+        <v>-8.586680227580267</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5481826610366212</v>
+        <v>-0.4859592779190702</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.327275380166182</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.496347730558376</v>
+        <v>1.552704009327075</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.500090291920285</v>
+        <v>-8.344531834126409</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.4368609492739348</v>
+        <v>-0.3746375661563839</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.327275380166182</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.510810084939519</v>
+        <v>1.567166363708218</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.436860920151938</v>
+        <v>-8.281302462358061</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.4170370801074008</v>
+        <v>-0.3548136969898499</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.327275380166182</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.505342205398714</v>
+        <v>1.561698484167413</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.313569785334808</v>
+        <v>-8.158011327540931</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3702225321699717</v>
+        <v>-0.3079991490524212</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.297911376630216</v>
+        <v>-2.203984245349052</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.576814980299569</v>
+        <v>1.633171259068268</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389905</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.292420586431366</v>
+        <v>-8.136862128637489</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3540618743712698</v>
+        <v>-0.2918384912537189</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.276762177726773</v>
+        <v>-2.182835046445609</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.59720547787896</v>
+        <v>1.653561756647659</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788089</v>
+        <v>3.74832483278809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-8.04865514444792</v>
+        <v>-7.893096686654045</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.2607749892308409</v>
+        <v>-0.1985516061132908</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.276762177726773</v>
+        <v>-2.182835046445609</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.592986186226011</v>
+        <v>1.64934246499471</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.78462707725466</v>
+        <v>-7.629068619460785</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1530394484335207</v>
+        <v>-0.09081606531597064</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.07489677891082</v>
+        <v>-1.980969647629655</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.716229739435599</v>
+        <v>1.772586018204298</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749179</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.534776683305585</v>
+        <v>-7.37921822551171</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.06035721587018861</v>
+        <v>0.001866167247360995</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.07489677891082</v>
+        <v>-1.980969647629655</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.708971814419301</v>
+        <v>1.765328093188</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.231209194301607</v>
+        <v>-7.075650736507732</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.06466890325205155</v>
+        <v>0.1268922863696016</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.07489677891082</v>
+        <v>-1.980969647629655</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.71257093793995</v>
+        <v>1.768927216708649</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.157729285449593</v>
+        <v>-7.002170827655718</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1073883728474105</v>
+        <v>0.1696117559649606</v>
       </c>
       <c r="F1921" t="n">
-        <v>-2.001416870058805</v>
+        <v>-1.907489738777641</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.769986389305712</v>
+        <v>1.826342668074411</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.93269628578077</v>
+        <v>-6.777137827986895</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.1964220503312371</v>
+        <v>0.2586454334487867</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.776383870389982</v>
+        <v>-1.682456739108818</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.904026666723303</v>
+        <v>1.960382945492002</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.718061908144363</v>
+        <v>-6.562503450350488</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.2869706024401171</v>
+        <v>0.3491939855576667</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.561749492753576</v>
+        <v>-1.467822361472411</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.037502094359464</v>
+        <v>2.093858373128163</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.451461551170011</v>
+        <v>-6.295903093376136</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3748050040136532</v>
+        <v>0.4370283871312033</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.561749492753576</v>
+        <v>-1.467822361472411</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.01869635314326</v>
+        <v>2.075052631911959</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.211031054365151</v>
+        <v>-6.055472596571276</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4727202793604746</v>
+        <v>0.5349436624780246</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.321318995948715</v>
+        <v>-1.227391864667551</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.164697727851054</v>
+        <v>2.221054006619752</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.968240246715705</v>
+        <v>-5.812681788921831</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.573765916255073</v>
+        <v>0.6359892993726231</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.321318995948715</v>
+        <v>-1.227391864667551</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.168627041685874</v>
+        <v>2.224983320454573</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.85230039709052</v>
+        <v>-5.696741939296645</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6208204400224875</v>
+        <v>0.6830438231400371</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.244497264932591</v>
+        <v>-1.150570133651427</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.215398664212888</v>
+        <v>2.271754942981587</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.609644808667356</v>
+        <v>-5.454086350873482</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7148807466117462</v>
+        <v>0.7771041297292962</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.244497264932591</v>
+        <v>-1.150570133651427</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.212396735432882</v>
+        <v>2.26875301420158</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145932</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.389624010630346</v>
+        <v>-5.234065552836471</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8044681028371645</v>
+        <v>0.8666914859547146</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.103277419864611</v>
+        <v>-1.009350288583447</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.298707679484284</v>
+        <v>2.355063958252983</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.843270952009946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.190375380725537</v>
+        <v>-5.034816922931662</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9000617376009115</v>
+        <v>0.9622851207184615</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.103277419864611</v>
+        <v>-1.009350288583447</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.314601862286107</v>
+        <v>2.370958141054806</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966253</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.030860277206167</v>
+        <v>-4.875301819412292</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9650136234489612</v>
+        <v>1.027237006566511</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.9437623163452412</v>
+        <v>-0.8498351850640767</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.411456768838031</v>
+        <v>2.46781304760673</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.79126997604699</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.88618813210643</v>
+        <v>-4.730629674312555</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.032970584050296</v>
+        <v>1.095193967167846</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7990901712455039</v>
+        <v>-0.7051630399643394</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.508348158459313</v>
+        <v>2.564704437228012</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.946062959464122</v>
+        <v>-4.790504501670247</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.995058144508645</v>
+        <v>1.057281527626195</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.858964998603196</v>
+        <v>-0.7650378673220315</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.458460753446124</v>
+        <v>2.514817032214823</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144509</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.859263461685114</v>
+        <v>-4.703705003891239</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.052178436942814</v>
+        <v>1.114401820060364</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.858964998603196</v>
+        <v>-0.7650378673220315</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.48086124676869</v>
+        <v>2.537217525537389</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.759570846956102</v>
+        <v>-4.604012389162227</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.092127884207831</v>
+        <v>1.154351267325381</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.7592723838741842</v>
+        <v>-0.6653452525930197</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.540749216979509</v>
+        <v>2.597105495748208</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473594</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.827941033280112</v>
+        <v>-4.672382575486237</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.075786732152929</v>
+        <v>1.138010115270479</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.6560695535568047</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.55732155887594</v>
+        <v>2.613677837644639</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978363</v>
+        <v>3.714175563978365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.706524603653635</v>
+        <v>-4.550966145859761</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.114790012635411</v>
+        <v>1.177013395752961</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.6560695535568047</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.547758267507831</v>
+        <v>2.60411454627653</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.737517762982341</v>
+        <v>-4.581959305188466</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.927102313944316</v>
+        <v>0.9893256970618658</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.6560695535568047</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.372467832548218</v>
+        <v>2.428824111316917</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675894</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.562043503189871</v>
+        <v>-4.406485045395996</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.001859249853092</v>
+        <v>1.064082632970641</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.6560695535568047</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.377035064540006</v>
+        <v>2.433391343308705</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.67297975583112</v>
+        <v>-4.517421298037245</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9574962226833894</v>
+        <v>1.019719605800939</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.6560695535568047</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.377046538426804</v>
+        <v>2.433402817195502</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581285</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.876006333374353</v>
+        <v>-4.720447875580478</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8794169768860018</v>
+        <v>0.9416403600035517</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.9530232623812026</v>
+        <v>-0.8590961311000381</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.258361977120769</v>
+        <v>2.314718255889468</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734154</v>
+        <v>3.784340376734158</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.71808073443906</v>
+        <v>-4.562522276645185</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9527596028922514</v>
+        <v>1.014982986009801</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.9530232623812026</v>
+        <v>-0.8590961311000381</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.268534363552901</v>
+        <v>2.3248906423216</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212291</v>
+        <v>3.786946382212294</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.866401988250189</v>
+        <v>-4.710843530456314</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8883773719416601</v>
+        <v>0.9506007550592102</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.9530232623812026</v>
+        <v>-0.8590961311000381</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.263480634126762</v>
+        <v>2.319836912895461</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786038</v>
+        <v>3.752023923786042</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.86758507290125</v>
+        <v>-4.712026615107375</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8796799135257616</v>
+        <v>0.9419032966433114</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.9586663108477141</v>
+        <v>-0.8647391795665497</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.251870580491381</v>
+        <v>2.308226859260079</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273184</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.744457365907166</v>
+        <v>-4.588898908113292</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9294828693564963</v>
+        <v>0.9917062524740463</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.9586663108477141</v>
+        <v>-0.8647391795665497</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.252422453524482</v>
+        <v>2.308778732293181</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279493</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.651646884456307</v>
+        <v>-4.496088426662432</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8958797538282057</v>
+        <v>0.9581031369457558</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8658558293968548</v>
+        <v>-0.7719286981156903</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.237381434286363</v>
+        <v>2.293737713055062</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.74828224103042</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.603083832235277</v>
+        <v>-4.447525374441402</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9171784506412186</v>
+        <v>0.9794018337587684</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8172927771758246</v>
+        <v>-0.7233656458946601</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.268392741543582</v>
+        <v>2.324749020312281</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.400130007456823</v>
+        <v>3.833384273749994</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.488951331662167</v>
+        <v>-4.334854156205152</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9579071593821855</v>
+        <v>1.019546029564992</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.703160276602715</v>
+        <v>-0.6106944276584099</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.331947950399171</v>
+        <v>2.387427459765754</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240429.xlsx
+++ b/tame_output/ON/bt/strategyON_20240429.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-23.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.7%</t>
+          <t>116.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>136.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.0%</t>
+          <t>-57.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.9%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-595.1%</t>
+          <t>-604.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-65.3%</t>
+          <t>-64.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-274.3%</t>
+          <t>-278.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-38.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-169.8%</t>
+          <t>-167.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-285.1%</t>
+          <t>-295.4%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-207.3%</t>
+          <t>-158.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1948"/>
+  <dimension ref="A1:G1949"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.30201228396238</v>
+        <v>-12.29179300885067</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.75940716244755</v>
+        <v>-1.755319452402868</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.606166793021496</v>
+        <v>-3.603483160699177</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9980540996382503</v>
+        <v>0.9996642790316415</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.24999676999356</v>
+        <v>-12.23977749488186</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.734610621173625</v>
+        <v>-1.730522911128942</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.606166793021496</v>
+        <v>-3.603483160699177</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.002044435324651</v>
+        <v>1.003654614718042</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.39166861171768</v>
+        <v>-12.38144933660598</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.792754584762014</v>
+        <v>-1.788666874717332</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.606166793021496</v>
+        <v>-3.603483160699177</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.000569208425909</v>
+        <v>1.002179387819301</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.49057535217696</v>
+        <v>-12.48035607706525</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.817263870780852</v>
+        <v>-1.813176160736169</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.705073533480772</v>
+        <v>-3.702389901158452</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9562785743152165</v>
+        <v>0.957888753708608</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.29142324493986</v>
+        <v>-12.28120396982815</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.750654161532696</v>
+        <v>-1.746566451488013</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.539751007530958</v>
+        <v>-3.537067375208639</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.042420956238421</v>
+        <v>1.044031135631813</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.06557809222045</v>
+        <v>-12.05535881710874</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.650737027408722</v>
+        <v>-1.64664931736404</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.497824331943795</v>
+        <v>-3.495140699621476</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.077156034626928</v>
+        <v>1.07876621402032</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.77930327989775</v>
+        <v>-11.76908400478605</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.535087957923585</v>
+        <v>-1.531000247878903</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.497824331943795</v>
+        <v>-3.495140699621476</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.078295179182987</v>
+        <v>1.079905358576378</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.83219856794204</v>
+        <v>-11.82197929283033</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.553612298979192</v>
+        <v>-1.54952458893451</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.492868985855349</v>
+        <v>-3.490185353533029</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.083902160998163</v>
+        <v>1.085512340391554</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.54828983701329</v>
+        <v>-11.53807056190159</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.434315102369056</v>
+        <v>-1.430227392324374</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.492868985855349</v>
+        <v>-3.490185353533029</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.089635865236799</v>
+        <v>1.091246044630191</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.4328689128752</v>
+        <v>-11.42264963776349</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.397883995107683</v>
+        <v>-1.393796285063001</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.377448061717253</v>
+        <v>-3.374764429394934</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.149151157325791</v>
+        <v>1.150761336719182</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.16903204567113</v>
+        <v>-11.15881277055942</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.302232729538962</v>
+        <v>-1.29814501949428</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.377448061717253</v>
+        <v>-3.374764429394934</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.139267676012884</v>
+        <v>1.140877855406275</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.90179024480273</v>
+        <v>-10.89157096969102</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.197170569690977</v>
+        <v>-1.193082859646295</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.377448061717253</v>
+        <v>-3.374764429394934</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.13743311551351</v>
+        <v>1.139043294906901</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.77848431632451</v>
+        <v>-10.7682650412128</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.148148513273151</v>
+        <v>-1.144060803228469</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.28803039058969</v>
+        <v>-3.285346758267371</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.190783403216587</v>
+        <v>1.192393582609978</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.75453077534855</v>
+        <v>-10.74431150023685</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.137898590737274</v>
+        <v>-1.133810880692592</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.264076849613732</v>
+        <v>-3.261393217291413</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.205824033947655</v>
+        <v>1.207434213341046</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.49047083702575</v>
+        <v>-10.48025156191405</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.045534931569907</v>
+        <v>-1.041447221525225</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.000016911290936</v>
+        <v>-2.997333278968617</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.350999680779581</v>
+        <v>1.352609860172972</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.783391213520916</v>
+        <v>-9.773171938409211</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.765490115828273</v>
+        <v>-0.7614024057835911</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.000016911290936</v>
+        <v>-2.997333278968617</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.34821264711928</v>
+        <v>1.349822826512671</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.743206915154726</v>
+        <v>-9.732987640043021</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7490727725939554</v>
+        <v>-0.7449850625492735</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.959832612924745</v>
+        <v>-2.957148980602426</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.372666850026836</v>
+        <v>1.374277029420227</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.663137119616922</v>
+        <v>-9.652917844505216</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7176780331580765</v>
+        <v>-0.7135903231133947</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.879762817386941</v>
+        <v>-2.877079185064622</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.420075548570275</v>
+        <v>1.421685727963666</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.429655897387324</v>
+        <v>-9.419436622275619</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6163611154283855</v>
+        <v>-0.6122734053837031</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.646281595157343</v>
+        <v>-2.643597962835023</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.568088710745886</v>
+        <v>1.569698890139278</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.24994736724345</v>
+        <v>-9.239728092131745</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5473699136837951</v>
+        <v>-0.5432822036391132</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.589110090994647</v>
+        <v>-2.586426458672328</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.599499402930545</v>
+        <v>1.601109582323936</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.117671893612563</v>
+        <v>-9.107452618500858</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4990922374844131</v>
+        <v>-0.4950045274397312</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.45683461736376</v>
+        <v>-2.454150985041441</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.674232173856104</v>
+        <v>1.675842353249495</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.92707221893941</v>
+        <v>-8.916852943827704</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4200373069275152</v>
+        <v>-0.4159495968828328</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.266234942690608</v>
+        <v>-2.263551310368288</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.791407039347632</v>
+        <v>1.793017218741023</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.678072420255829</v>
+        <v>-8.667853145144123</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3075310462304239</v>
+        <v>-0.3034433361857416</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.266234942690608</v>
+        <v>-2.263551310368288</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.804313380571291</v>
+        <v>1.805923559964682</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.783662410028933</v>
+        <v>-8.773443134917228</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4777429717388841</v>
+        <v>-0.4736552616942022</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.371824932463712</v>
+        <v>-2.369141300141393</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.612983457108209</v>
+        <v>1.614593636501601</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.80239731214753</v>
+        <v>-8.792178037035825</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4366925907092369</v>
+        <v>-0.4326048806645546</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.371824932463712</v>
+        <v>-2.369141300141393</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.661527798985296</v>
+        <v>1.663137978378687</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.654457270739931</v>
+        <v>-8.644237995628226</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4973954968343648</v>
+        <v>-0.4933077867896825</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.351504016555154</v>
+        <v>-2.348820384232835</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.553841425842263</v>
+        <v>1.555451605235654</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.630228634350958</v>
+        <v>-8.620009359239253</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4964180285322537</v>
+        <v>-0.4923303184875718</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.327275380166182</v>
+        <v>-2.324591747843863</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.559664621422168</v>
+        <v>1.561274800815559</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.586680227580267</v>
+        <v>-8.576460952468562</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4859592779190702</v>
+        <v>-0.4818715678743883</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.327275380166182</v>
+        <v>-2.324591747843863</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.552704009327075</v>
+        <v>1.554314188720466</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.344531834126409</v>
+        <v>-8.334312559014704</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3746375661563839</v>
+        <v>-0.370549856111702</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.327275380166182</v>
+        <v>-2.324591747843863</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.567166363708218</v>
+        <v>1.568776543101609</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.281302462358061</v>
+        <v>-8.271083187246356</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3548136969898499</v>
+        <v>-0.350725986945168</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.327275380166182</v>
+        <v>-2.324591747843863</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.561698484167413</v>
+        <v>1.563308663560804</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.158011327540931</v>
+        <v>-8.147792052429226</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3079991490524212</v>
+        <v>-0.3039114390077393</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.203984245349052</v>
+        <v>-2.201300613026733</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.633171259068268</v>
+        <v>1.634781438461659</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.136862128637489</v>
+        <v>-8.126642853525784</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2918384912537189</v>
+        <v>-0.287750781209037</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.182835046445609</v>
+        <v>-2.180151414123289</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.653561756647659</v>
+        <v>1.655171936041051</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.893096686654045</v>
+        <v>-7.882877411542339</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1985516061132908</v>
+        <v>-0.1944638960686085</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.182835046445609</v>
+        <v>-2.180151414123289</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.64934246499471</v>
+        <v>1.650952644388101</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.629068619460785</v>
+        <v>-7.61884934434908</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.09081606531597064</v>
+        <v>-0.08672835527128875</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.980969647629655</v>
+        <v>-1.978286015307336</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.772586018204298</v>
+        <v>1.774196197597689</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.37921822551171</v>
+        <v>-7.368998950400005</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.001866167247360995</v>
+        <v>0.00595387729204333</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.980969647629655</v>
+        <v>-1.978286015307336</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.765328093188</v>
+        <v>1.766938272581392</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.075650736507732</v>
+        <v>-7.065431461396027</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1268922863696016</v>
+        <v>0.1309799964142835</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.980969647629655</v>
+        <v>-1.978286015307336</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.768927216708649</v>
+        <v>1.77053739610204</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.002170827655718</v>
+        <v>-6.991951552544013</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1696117559649606</v>
+        <v>0.1736994660096429</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.907489738777641</v>
+        <v>-1.904806106455321</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.826342668074411</v>
+        <v>1.827952847467803</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.777137827986895</v>
+        <v>-6.76691855287519</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2586454334487867</v>
+        <v>0.262733143493469</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.682456739108818</v>
+        <v>-1.679773106786499</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.960382945492002</v>
+        <v>1.961993124885393</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.562503450350488</v>
+        <v>-6.552284175238783</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3491939855576667</v>
+        <v>0.353281695602349</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.467822361472411</v>
+        <v>-1.465138729150092</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.093858373128163</v>
+        <v>2.095468552521555</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.295903093376136</v>
+        <v>-6.285683818264431</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4370283871312033</v>
+        <v>0.4411160971758852</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.467822361472411</v>
+        <v>-1.465138729150092</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.075052631911959</v>
+        <v>2.07666281130535</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.055472596571276</v>
+        <v>-6.045253321459571</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5349436624780246</v>
+        <v>0.5390313725227069</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.227391864667551</v>
+        <v>-1.224708232345232</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.221054006619752</v>
+        <v>2.222664186013144</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.812681788921831</v>
+        <v>-5.802462513810125</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6359892993726231</v>
+        <v>0.6400770094173054</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.227391864667551</v>
+        <v>-1.224708232345232</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.224983320454573</v>
+        <v>2.226593499847964</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.696741939296645</v>
+        <v>-5.68652266418494</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6830438231400371</v>
+        <v>0.6871315331847194</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.150570133651427</v>
+        <v>-1.147886501329108</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.271754942981587</v>
+        <v>2.273365122374978</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.454086350873482</v>
+        <v>-5.443867075761776</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7771041297292962</v>
+        <v>0.7811918397739781</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.150570133651427</v>
+        <v>-1.147886501329108</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.26875301420158</v>
+        <v>2.270363193594972</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.234065552836471</v>
+        <v>-5.223846277724766</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8666914859547146</v>
+        <v>0.8707791959993965</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.009350288583447</v>
+        <v>-1.006666656261128</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.355063958252983</v>
+        <v>2.356674137646374</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.034816922931662</v>
+        <v>-5.024597647819957</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9622851207184615</v>
+        <v>0.9663728307631434</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.009350288583447</v>
+        <v>-1.006666656261128</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.370958141054806</v>
+        <v>2.372568320448197</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.875301819412292</v>
+        <v>-4.865082544300587</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.027237006566511</v>
+        <v>1.031324716611193</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8498351850640767</v>
+        <v>-0.8471515527417576</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.46781304760673</v>
+        <v>2.469423227000121</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.730629674312555</v>
+        <v>-4.720410399200849</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.095193967167846</v>
+        <v>1.099281677212528</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7051630399643394</v>
+        <v>-0.7024794076420202</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.564704437228012</v>
+        <v>2.566314616621403</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.790504501670247</v>
+        <v>-4.780285226558542</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.057281527626195</v>
+        <v>1.061369237670877</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7650378673220315</v>
+        <v>-0.7623542349997123</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.514817032214823</v>
+        <v>2.516427211608214</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.703705003891239</v>
+        <v>-4.693485728779534</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.114401820060364</v>
+        <v>1.118489530105047</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7650378673220315</v>
+        <v>-0.7623542349997123</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.537217525537389</v>
+        <v>2.53882770493078</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.604012389162227</v>
+        <v>-4.593793114050522</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.154351267325381</v>
+        <v>1.158438977370063</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6653452525930197</v>
+        <v>-0.6626616202707005</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.597105495748208</v>
+        <v>2.598715675141599</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.672382575486237</v>
+        <v>-4.662163300374532</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.138010115270479</v>
+        <v>1.142097825315161</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6560695535568047</v>
+        <v>-0.6533859212344856</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.613677837644639</v>
+        <v>2.61528801703803</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.550966145859761</v>
+        <v>-4.540746870748055</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.177013395752961</v>
+        <v>1.181101105797643</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6560695535568047</v>
+        <v>-0.6533859212344856</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.60411454627653</v>
+        <v>2.605724725669921</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.581959305188466</v>
+        <v>-4.571740030076761</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9893256970618658</v>
+        <v>0.9934134071065479</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6560695535568047</v>
+        <v>-0.6533859212344856</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.428824111316917</v>
+        <v>2.430434290710308</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.406485045395996</v>
+        <v>-4.396265770284291</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.064082632970641</v>
+        <v>1.068170343015324</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6560695535568047</v>
+        <v>-0.6533859212344856</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.433391343308705</v>
+        <v>2.435001522702096</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.517421298037245</v>
+        <v>-4.50720202292554</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.019719605800939</v>
+        <v>1.023807315845622</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6560695535568047</v>
+        <v>-0.6533859212344856</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.433402817195502</v>
+        <v>2.435012996588894</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.720447875580478</v>
+        <v>-4.710228600468773</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9416403600035517</v>
+        <v>0.9457280700482338</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8590961311000381</v>
+        <v>-0.856412498777719</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.314718255889468</v>
+        <v>2.316328435282859</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.562522276645185</v>
+        <v>-4.55230300153348</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.014982986009801</v>
+        <v>1.019070696054483</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8590961311000381</v>
+        <v>-0.856412498777719</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.3248906423216</v>
+        <v>2.326500821714991</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.710843530456314</v>
+        <v>-4.700624255344609</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9506007550592102</v>
+        <v>0.9546884651038923</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8590961311000381</v>
+        <v>-0.856412498777719</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.319836912895461</v>
+        <v>2.321447092288852</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.712026615107375</v>
+        <v>-4.701807339995669</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9419032966433114</v>
+        <v>0.9459910066879935</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8647391795665497</v>
+        <v>-0.8620555472442305</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.308226859260079</v>
+        <v>2.309837038653471</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.588898908113292</v>
+        <v>-4.578679633001586</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9917062524740463</v>
+        <v>0.9957939625187282</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8647391795665497</v>
+        <v>-0.8620555472442305</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.308778732293181</v>
+        <v>2.310388911686572</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.496088426662432</v>
+        <v>-4.485869151550727</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9581031369457558</v>
+        <v>0.9621908469904379</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7719286981156903</v>
+        <v>-0.7692450657933712</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.293737713055062</v>
+        <v>2.295347892448453</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.447525374441402</v>
+        <v>-4.437306099329697</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9794018337587684</v>
+        <v>0.9834895438034505</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.7233656458946601</v>
+        <v>-0.720682013572341</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.324749020312281</v>
+        <v>2.326359199705673</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,45 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.833384273749994</v>
+        <v>3.721073619942734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.334854156205152</v>
+        <v>-4.430790940700218</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.019546029564992</v>
+        <v>0.981171315766965</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.6106944276584099</v>
+        <v>-0.7141668549428619</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.387427459765754</v>
+        <v>2.325344003395083</v>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" s="2" t="n">
+        <v>45411</v>
+      </c>
+      <c r="B1949" t="n">
+        <v>3.836525561892339</v>
+      </c>
+      <c r="C1949" t="n">
+        <v>2.885809789519812</v>
+      </c>
+      <c r="D1949" t="n">
+        <v>-4.430790940700218</v>
+      </c>
+      <c r="E1949" t="n">
+        <v>0.981171315766965</v>
+      </c>
+      <c r="F1949" t="n">
+        <v>-0.7141668549428619</v>
+      </c>
+      <c r="G1949" t="n">
+        <v>2.87887358650618</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240429.xlsx
+++ b/tame_output/ON/bt/strategyON_20240429.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.5%</t>
+          <t>116.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.9%</t>
+          <t>-58.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.6%</t>
+          <t>444.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-604.7%</t>
+          <t>-595.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,22 +1175,22 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-64.0%</t>
+          <t>-66.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-278.1%</t>
+          <t>-274.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.2%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-295.4%</t>
+          <t>-285.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.29179300885067</v>
+        <v>-12.30201228396238</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.755319452402868</v>
+        <v>-1.75940716244755</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.603483160699177</v>
+        <v>-3.606166793021496</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9996642790316415</v>
+        <v>0.9980540996382503</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.23977749488186</v>
+        <v>-12.24999676999356</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.730522911128942</v>
+        <v>-1.734610621173625</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.603483160699177</v>
+        <v>-3.606166793021496</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.003654614718042</v>
+        <v>1.002044435324651</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.38144933660598</v>
+        <v>-12.39166861171768</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.788666874717332</v>
+        <v>-1.792754584762014</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.603483160699177</v>
+        <v>-3.606166793021496</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.002179387819301</v>
+        <v>1.000569208425909</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.48035607706525</v>
+        <v>-12.49057535217696</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.813176160736169</v>
+        <v>-1.817263870780852</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.702389901158452</v>
+        <v>-3.705073533480772</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.957888753708608</v>
+        <v>0.9562785743152165</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.28120396982815</v>
+        <v>-12.29142324493986</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.746566451488013</v>
+        <v>-1.750654161532696</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.537067375208639</v>
+        <v>-3.539751007530958</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.044031135631813</v>
+        <v>1.042420956238421</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.05535881710874</v>
+        <v>-12.06557809222045</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.64664931736404</v>
+        <v>-1.650737027408722</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.495140699621476</v>
+        <v>-3.497824331943795</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.07876621402032</v>
+        <v>1.077156034626928</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.76908400478605</v>
+        <v>-11.77930327989775</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.531000247878903</v>
+        <v>-1.535087957923585</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.495140699621476</v>
+        <v>-3.497824331943795</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.079905358576378</v>
+        <v>1.078295179182987</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.82197929283033</v>
+        <v>-11.83219856794204</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.54952458893451</v>
+        <v>-1.553612298979192</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.490185353533029</v>
+        <v>-3.492868985855349</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.085512340391554</v>
+        <v>1.083902160998163</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.53807056190159</v>
+        <v>-11.54828983701329</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.430227392324374</v>
+        <v>-1.434315102369056</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.490185353533029</v>
+        <v>-3.492868985855349</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.091246044630191</v>
+        <v>1.089635865236799</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.42264963776349</v>
+        <v>-11.4328689128752</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.393796285063001</v>
+        <v>-1.397883995107683</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.374764429394934</v>
+        <v>-3.377448061717253</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.150761336719182</v>
+        <v>1.149151157325791</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.15881277055942</v>
+        <v>-11.16903204567113</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.29814501949428</v>
+        <v>-1.302232729538962</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.374764429394934</v>
+        <v>-3.377448061717253</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.140877855406275</v>
+        <v>1.139267676012884</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.89157096969102</v>
+        <v>-10.90179024480273</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.193082859646295</v>
+        <v>-1.197170569690977</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.374764429394934</v>
+        <v>-3.377448061717253</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.139043294906901</v>
+        <v>1.13743311551351</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.7682650412128</v>
+        <v>-10.77848431632451</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.144060803228469</v>
+        <v>-1.148148513273151</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.285346758267371</v>
+        <v>-3.28803039058969</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.192393582609978</v>
+        <v>1.190783403216587</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.74431150023685</v>
+        <v>-10.75453077534855</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.133810880692592</v>
+        <v>-1.137898590737274</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.261393217291413</v>
+        <v>-3.264076849613732</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.207434213341046</v>
+        <v>1.205824033947655</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.48025156191405</v>
+        <v>-10.49047083702575</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.041447221525225</v>
+        <v>-1.045534931569907</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.997333278968617</v>
+        <v>-3.000016911290936</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.352609860172972</v>
+        <v>1.350999680779581</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.773171938409211</v>
+        <v>-9.783391213520916</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7614024057835911</v>
+        <v>-0.765490115828273</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.997333278968617</v>
+        <v>-3.000016911290936</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.349822826512671</v>
+        <v>1.34821264711928</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.732987640043021</v>
+        <v>-9.743206915154726</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7449850625492735</v>
+        <v>-0.7490727725939554</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.957148980602426</v>
+        <v>-2.959832612924745</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.374277029420227</v>
+        <v>1.372666850026836</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.652917844505216</v>
+        <v>-9.663137119616922</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7135903231133947</v>
+        <v>-0.7176780331580765</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.877079185064622</v>
+        <v>-2.879762817386941</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.421685727963666</v>
+        <v>1.420075548570275</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.419436622275619</v>
+        <v>-9.429655897387324</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6122734053837031</v>
+        <v>-0.6163611154283855</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.643597962835023</v>
+        <v>-2.646281595157343</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.569698890139278</v>
+        <v>1.568088710745886</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.239728092131745</v>
+        <v>-9.24994736724345</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5432822036391132</v>
+        <v>-0.5473699136837951</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.586426458672328</v>
+        <v>-2.589110090994647</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.601109582323936</v>
+        <v>1.599499402930545</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.107452618500858</v>
+        <v>-9.117671893612563</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4950045274397312</v>
+        <v>-0.4990922374844131</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.454150985041441</v>
+        <v>-2.45683461736376</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.675842353249495</v>
+        <v>1.674232173856104</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.916852943827704</v>
+        <v>-8.92707221893941</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4159495968828328</v>
+        <v>-0.4200373069275152</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.263551310368288</v>
+        <v>-2.266234942690608</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.793017218741023</v>
+        <v>1.791407039347632</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.667853145144123</v>
+        <v>-8.678072420255829</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3034433361857416</v>
+        <v>-0.3075310462304239</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.263551310368288</v>
+        <v>-2.266234942690608</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.805923559964682</v>
+        <v>1.804313380571291</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.773443134917228</v>
+        <v>-8.783662410028933</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4736552616942022</v>
+        <v>-0.4777429717388841</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.369141300141393</v>
+        <v>-2.371824932463712</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.614593636501601</v>
+        <v>1.612983457108209</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.792178037035825</v>
+        <v>-8.80239731214753</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4326048806645546</v>
+        <v>-0.4366925907092369</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.369141300141393</v>
+        <v>-2.371824932463712</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.663137978378687</v>
+        <v>1.661527798985296</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.644237995628226</v>
+        <v>-8.654457270739931</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4933077867896825</v>
+        <v>-0.4973954968343648</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.348820384232835</v>
+        <v>-2.351504016555154</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.555451605235654</v>
+        <v>1.553841425842263</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.620009359239253</v>
+        <v>-8.630228634350958</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4923303184875718</v>
+        <v>-0.4964180285322537</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.324591747843863</v>
+        <v>-2.327275380166182</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.561274800815559</v>
+        <v>1.559664621422168</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.576460952468562</v>
+        <v>-8.586680227580267</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4818715678743883</v>
+        <v>-0.4859592779190702</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.324591747843863</v>
+        <v>-2.327275380166182</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.554314188720466</v>
+        <v>1.552704009327075</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.334312559014704</v>
+        <v>-8.344531834126409</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.370549856111702</v>
+        <v>-0.3746375661563839</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.324591747843863</v>
+        <v>-2.327275380166182</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.568776543101609</v>
+        <v>1.567166363708218</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.271083187246356</v>
+        <v>-8.281302462358061</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.350725986945168</v>
+        <v>-0.3548136969898499</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.324591747843863</v>
+        <v>-2.327275380166182</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.563308663560804</v>
+        <v>1.561698484167413</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.147792052429226</v>
+        <v>-8.158011327540931</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3039114390077393</v>
+        <v>-0.3079991490524212</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.201300613026733</v>
+        <v>-2.203984245349052</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.634781438461659</v>
+        <v>1.633171259068268</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.126642853525784</v>
+        <v>-8.136862128637489</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.287750781209037</v>
+        <v>-0.2918384912537189</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.180151414123289</v>
+        <v>-2.182835046445609</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.655171936041051</v>
+        <v>1.653561756647659</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832483278809</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.882877411542339</v>
+        <v>-7.893096686654045</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1944638960686085</v>
+        <v>-0.1985516061132908</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.180151414123289</v>
+        <v>-2.182835046445609</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.650952644388101</v>
+        <v>1.64934246499471</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.61884934434908</v>
+        <v>-7.629068619460785</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.08672835527128875</v>
+        <v>-0.09081606531597064</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.978286015307336</v>
+        <v>-1.980969647629655</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.774196197597689</v>
+        <v>1.772586018204298</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.368998950400005</v>
+        <v>-7.37921822551171</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.00595387729204333</v>
+        <v>0.001866167247360995</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.978286015307336</v>
+        <v>-1.980969647629655</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.766938272581392</v>
+        <v>1.765328093188</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.065431461396027</v>
+        <v>-7.075650736507732</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1309799964142835</v>
+        <v>0.1268922863696016</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.978286015307336</v>
+        <v>-1.980969647629655</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.77053739610204</v>
+        <v>1.768927216708649</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.991951552544013</v>
+        <v>-7.002170827655718</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1736994660096429</v>
+        <v>0.1696117559649606</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.904806106455321</v>
+        <v>-1.907489738777641</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.827952847467803</v>
+        <v>1.826342668074411</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.76691855287519</v>
+        <v>-6.777137827986895</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.262733143493469</v>
+        <v>0.2586454334487867</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.679773106786499</v>
+        <v>-1.682456739108818</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.961993124885393</v>
+        <v>1.960382945492002</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.552284175238783</v>
+        <v>-6.562503450350488</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.353281695602349</v>
+        <v>0.3491939855576667</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.465138729150092</v>
+        <v>-1.467822361472411</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.095468552521555</v>
+        <v>2.093858373128163</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.285683818264431</v>
+        <v>-6.295903093376136</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4411160971758852</v>
+        <v>0.4370283871312033</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.465138729150092</v>
+        <v>-1.467822361472411</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.07666281130535</v>
+        <v>2.075052631911959</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.045253321459571</v>
+        <v>-6.055472596571276</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5390313725227069</v>
+        <v>0.5349436624780246</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.224708232345232</v>
+        <v>-1.227391864667551</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.222664186013144</v>
+        <v>2.221054006619752</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.802462513810125</v>
+        <v>-5.812681788921831</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6400770094173054</v>
+        <v>0.6359892993726231</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.224708232345232</v>
+        <v>-1.227391864667551</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.226593499847964</v>
+        <v>2.224983320454573</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.68652266418494</v>
+        <v>-5.696741939296645</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6871315331847194</v>
+        <v>0.6830438231400371</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.147886501329108</v>
+        <v>-1.150570133651427</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.273365122374978</v>
+        <v>2.271754942981587</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.443867075761776</v>
+        <v>-5.454086350873482</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7811918397739781</v>
+        <v>0.7771041297292962</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.147886501329108</v>
+        <v>-1.150570133651427</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.270363193594972</v>
+        <v>2.26875301420158</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.223846277724766</v>
+        <v>-5.234065552836471</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8707791959993965</v>
+        <v>0.8666914859547146</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.006666656261128</v>
+        <v>-1.009350288583447</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.356674137646374</v>
+        <v>2.355063958252983</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.024597647819957</v>
+        <v>-5.034816922931662</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9663728307631434</v>
+        <v>0.9622851207184615</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.006666656261128</v>
+        <v>-1.009350288583447</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.372568320448197</v>
+        <v>2.370958141054806</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.865082544300587</v>
+        <v>-4.875301819412292</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.031324716611193</v>
+        <v>1.027237006566511</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8471515527417576</v>
+        <v>-0.8498351850640767</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.469423227000121</v>
+        <v>2.46781304760673</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.720410399200849</v>
+        <v>-4.730629674312555</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.099281677212528</v>
+        <v>1.095193967167846</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7024794076420202</v>
+        <v>-0.7051630399643394</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.566314616621403</v>
+        <v>2.564704437228012</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.780285226558542</v>
+        <v>-4.790504501670247</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.061369237670877</v>
+        <v>1.057281527626195</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7623542349997123</v>
+        <v>-0.7650378673220315</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.516427211608214</v>
+        <v>2.514817032214823</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.693485728779534</v>
+        <v>-4.703705003891239</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.118489530105047</v>
+        <v>1.114401820060364</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7623542349997123</v>
+        <v>-0.7650378673220315</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.53882770493078</v>
+        <v>2.537217525537389</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.593793114050522</v>
+        <v>-4.604012389162227</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.158438977370063</v>
+        <v>1.154351267325381</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6626616202707005</v>
+        <v>-0.6653452525930197</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.598715675141599</v>
+        <v>2.597105495748208</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.662163300374532</v>
+        <v>-4.672382575486237</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.142097825315161</v>
+        <v>1.138010115270479</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6533859212344856</v>
+        <v>-0.6560695535568047</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.61528801703803</v>
+        <v>2.613677837644639</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978365</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.540746870748055</v>
+        <v>-4.550966145859761</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.181101105797643</v>
+        <v>1.177013395752961</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6533859212344856</v>
+        <v>-0.6560695535568047</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.605724725669921</v>
+        <v>2.60411454627653</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.571740030076761</v>
+        <v>-4.581959305188466</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9934134071065479</v>
+        <v>0.9893256970618658</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6533859212344856</v>
+        <v>-0.6560695535568047</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.430434290710308</v>
+        <v>2.428824111316917</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.396265770284291</v>
+        <v>-4.406485045395996</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.068170343015324</v>
+        <v>1.064082632970641</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6533859212344856</v>
+        <v>-0.6560695535568047</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.435001522702096</v>
+        <v>2.433391343308705</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.50720202292554</v>
+        <v>-4.517421298037245</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.023807315845622</v>
+        <v>1.019719605800939</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6533859212344856</v>
+        <v>-0.6560695535568047</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.435012996588894</v>
+        <v>2.433402817195502</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.710228600468773</v>
+        <v>-4.720447875580478</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9457280700482338</v>
+        <v>0.9416403600035517</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.856412498777719</v>
+        <v>-0.8590961311000381</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.316328435282859</v>
+        <v>2.314718255889468</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734158</v>
+        <v>3.784340376734156</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.55230300153348</v>
+        <v>-4.562522276645185</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.019070696054483</v>
+        <v>1.014982986009801</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.856412498777719</v>
+        <v>-0.8590961311000381</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.326500821714991</v>
+        <v>2.3248906423216</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212294</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.700624255344609</v>
+        <v>-4.710843530456314</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9546884651038923</v>
+        <v>0.9506007550592102</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.856412498777719</v>
+        <v>-0.8590961311000381</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.321447092288852</v>
+        <v>2.319836912895461</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786042</v>
+        <v>3.75202392378604</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.701807339995669</v>
+        <v>-4.712026615107375</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9459910066879935</v>
+        <v>0.9419032966433114</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8620555472442305</v>
+        <v>-0.8647391795665497</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.309837038653471</v>
+        <v>2.308226859260079</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273185</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.578679633001586</v>
+        <v>-4.588898908113292</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9957939625187282</v>
+        <v>0.9917062524740463</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8620555472442305</v>
+        <v>-0.8647391795665497</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.310388911686572</v>
+        <v>2.308778732293181</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.485869151550727</v>
+        <v>-4.496088426662432</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9621908469904379</v>
+        <v>0.9581031369457558</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7692450657933712</v>
+        <v>-0.7719286981156903</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.295347892448453</v>
+        <v>2.293737713055062</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.437306099329697</v>
+        <v>-4.447525374441402</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9834895438034505</v>
+        <v>0.9794018337587684</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.720682013572341</v>
+        <v>-0.7233656458946601</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.326359199705673</v>
+        <v>2.324749020312281</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942734</v>
+        <v>3.721073619942731</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.430790940700218</v>
+        <v>-4.334854156205152</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.981171315766965</v>
+        <v>1.019546029564992</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.7141668549428619</v>
+        <v>-0.6106944276584099</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.325344003395083</v>
+        <v>2.387427459765754</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,19 +46372,19 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.836525561892339</v>
+        <v>3.836525561892337</v>
       </c>
       <c r="C1949" t="n">
         <v>2.885809789519812</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.430790940700218</v>
+        <v>-4.334854156205152</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.981171315766965</v>
+        <v>1.019546029564992</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.7141668549428619</v>
+        <v>-0.6106944276584099</v>
       </c>
       <c r="G1949" t="n">
         <v>2.87887358650618</v>

--- a/tame_output/ON/bt/strategyON_20240429.xlsx
+++ b/tame_output/ON/bt/strategyON_20240429.xlsx
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.74832483278809</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734156</v>
+        <v>3.784340376734158</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212294</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202392378604</v>
+        <v>3.752023923786042</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273185</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030422</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942731</v>
+        <v>3.721073619942733</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.836525561892337</v>
+        <v>3.836525561892339</v>
       </c>
       <c r="C1949" t="n">
         <v>2.885809789519812</v>

--- a/tame_output/ON/bt/strategyON_20240429.xlsx
+++ b/tame_output/ON/bt/strategyON_20240429.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>27.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-41.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-81.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.6%</t>
+          <t>116.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.5%</t>
+          <t>137.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-720.6%</t>
+          <t>-730.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.0%</t>
+          <t>-58.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.8%</t>
+          <t>439.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-595.1%</t>
+          <t>-629.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-288.6%</t>
+          <t>-292.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-46.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-66.0%</t>
+          <t>521.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-274.3%</t>
+          <t>-288.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.4%</t>
+          <t>-167.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-285.1%</t>
+          <t>-294.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-158.1%</t>
+          <t>-176.1%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6091471528189167</v>
+        <v>-0.7053466378184676</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.877313476885412</v>
+        <v>2.838833682885591</v>
       </c>
       <c r="F1845" t="n">
         <v>1.525689399526259</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.8167129372105286</v>
+        <v>-0.9129124222100795</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.792111959248007</v>
+        <v>2.753632165248187</v>
       </c>
       <c r="F1846" t="n">
         <v>1.318123615134647</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.234466960757366</v>
+        <v>-1.330666445756916</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.622937241334336</v>
+        <v>2.584457447334516</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9003695915878102</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.456088894315483</v>
+        <v>-1.552288379315034</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.53415468451001</v>
+        <v>2.49567489051019</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8628434579004411</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.66409295266856</v>
+        <v>-1.760292437668111</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.455845205722705</v>
+        <v>2.417365411722884</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8628434579004411</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.875505373556535</v>
+        <v>-1.971704858556086</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.366361693705503</v>
+        <v>2.327881899705683</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6514310370124661</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.214663751145058</v>
+        <v>-2.310863236144608</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.223782641976543</v>
+        <v>2.185302847976723</v>
       </c>
       <c r="F1851" t="n">
         <v>0.312272659423944</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.542680972872537</v>
+        <v>-2.638880457872087</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.11291404302432</v>
+        <v>2.0744342490245</v>
       </c>
       <c r="F1852" t="n">
         <v>-0.01574456230353516</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.036005844407715</v>
+        <v>-3.132205329407265</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.923682844818817</v>
+        <v>1.885203050818997</v>
       </c>
       <c r="F1853" t="n">
         <v>-0.1207306765431539</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.528390872431812</v>
+        <v>-3.624590357431362</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.727835225652911</v>
+        <v>1.689355431653091</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.6131157045672506</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.913571263361884</v>
+        <v>-4.009770748361435</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.572305608093745</v>
+        <v>1.533825814093925</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.6131157045672506</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.257254036588547</v>
+        <v>-4.353453521588097</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.436601622257696</v>
+        <v>1.398121828257876</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.7210217565944688</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.614904386826895</v>
+        <v>-4.711103871826445</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.289647540818615</v>
+        <v>1.251167746818795</v>
       </c>
       <c r="F1857" t="n">
         <v>-1.078672106832817</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.924138489822946</v>
+        <v>-5.020337974822496</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.167726826320454</v>
+        <v>1.129247032320634</v>
       </c>
       <c r="F1858" t="n">
         <v>-1.078672106832817</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.355944282972733</v>
+        <v>-5.452143767972284</v>
       </c>
       <c r="E1859" t="n">
-        <v>0.9813373965279433</v>
+        <v>0.942857602528123</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.215089603274084</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.590638277105286</v>
+        <v>-5.686837762104836</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.8757445738770131</v>
+        <v>0.8372647798771928</v>
       </c>
       <c r="F1860" t="n">
         <v>-1.208753336044829</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.926300924335738</v>
+        <v>-6.022500409335288</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7400601066407972</v>
+        <v>0.701580312640977</v>
       </c>
       <c r="F1861" t="n">
         <v>-1.208753336044829</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.289927169236051</v>
+        <v>-6.386126654235602</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6010971689149134</v>
+        <v>0.5626173749150931</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.306974972911954</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.655054551874798</v>
+        <v>-6.751254036874348</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.454300730865246</v>
+        <v>0.4158209368654258</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.603285757210967</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-7.063643329055477</v>
+        <v>-7.159842814055027</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.2896267640077337</v>
+        <v>0.2511469700079134</v>
       </c>
       <c r="F1864" t="n">
         <v>-2.011874534391645</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.476625813196571</v>
+        <v>-7.572825298196121</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1196192028227565</v>
+        <v>0.08113940882293669</v>
       </c>
       <c r="F1865" t="n">
         <v>-2.011874534391645</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.893017687483568</v>
+        <v>-7.989217172483118</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.04894349628316519</v>
+        <v>-0.08742329028298501</v>
       </c>
       <c r="F1866" t="n">
         <v>-2.011874534391645</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.269694698013412</v>
+        <v>-8.365894183012962</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1893556098264235</v>
+        <v>-0.2278354038262433</v>
       </c>
       <c r="F1867" t="n">
         <v>-2.011874534391645</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.615569519998221</v>
+        <v>-8.711769004997771</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.3316059734746521</v>
+        <v>-0.370085767474472</v>
       </c>
       <c r="F1868" t="n">
         <v>-2.011874534391645</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.777711790461314</v>
+        <v>-8.873911275460864</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3980579616048883</v>
+        <v>-0.4365377556047085</v>
       </c>
       <c r="F1869" t="n">
         <v>-2.011874534391645</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-9.074373132271512</v>
+        <v>-9.170572617271063</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.5129435223997594</v>
+        <v>-0.5514233163995796</v>
       </c>
       <c r="F1870" t="n">
         <v>-2.080617670125524</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.507722240381748</v>
+        <v>-9.603921725381298</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6903094701782564</v>
+        <v>-0.7287892641780767</v>
       </c>
       <c r="F1871" t="n">
         <v>-2.080617670125524</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.890723629124379</v>
+        <v>-9.986923114123929</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.8436121269968933</v>
+        <v>-0.8820919209967131</v>
       </c>
       <c r="F1872" t="n">
         <v>-2.080617670125524</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.0481225093375</v>
+        <v>-10.14432199433705</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9040001631107111</v>
+        <v>-0.9424799571105313</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.238016550338645</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.4076528318415</v>
+        <v>-10.50385231684105</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.042461988814262</v>
+        <v>-1.080941782814082</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.238016550338645</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.73405286050651</v>
+        <v>-10.83025234550606</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.165105980323089</v>
+        <v>-1.20358577432291</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.564416579003658</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.95320182858071</v>
+        <v>-11.04940131358026</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.249723816930999</v>
+        <v>-1.288203610930819</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.783565547077855</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.9495109036243</v>
+        <v>-11.04571038862385</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.248247446948435</v>
+        <v>-1.286727240948256</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.783565547077855</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.15376907895416</v>
+        <v>-11.24996856395371</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.324437519961738</v>
+        <v>-1.362917313961558</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.911204491691844</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.37180685058534</v>
+        <v>-11.46800633558489</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.407170074129774</v>
+        <v>-1.445649868129593</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.085975259787743</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.29833701891789</v>
+        <v>-11.39453650391744</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.362410439969373</v>
+        <v>-1.400890233969193</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.012505428120295</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.47346143630444</v>
+        <v>-11.56966092130399</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.417904986176473</v>
+        <v>-1.456384780176293</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.187629845506839</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.70791353031893</v>
+        <v>-11.80411301531848</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.518904988683865</v>
+        <v>-1.557384782683685</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.187629845506839</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.99571737485616</v>
+        <v>-12.09191685985571</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.640698717272736</v>
+        <v>-1.679178511272557</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.475433690044077</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.22554182201999</v>
+        <v>-12.32174130701954</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.731512706299711</v>
+        <v>-1.769992500299531</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.638081227114237</v>
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.30201228396238</v>
+        <v>-12.5537702267558</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.75940716244755</v>
+        <v>-1.86011033956492</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.606166793021496</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9980540996382503</v>
+        <v>0.9416978208695514</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.24999676999356</v>
+        <v>-12.50175471278699</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.734610621173625</v>
+        <v>-1.835313798290994</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.606166793021496</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.002044435324651</v>
+        <v>0.9456881565559523</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.39166861171768</v>
+        <v>-12.64342655451111</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.792754584762014</v>
+        <v>-1.893457761879384</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.606166793021496</v>
+        <v>-3.70009392430266</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.000569208425909</v>
+        <v>0.9442129296572106</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.49057535217696</v>
+        <v>-12.74233329497038</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.817263870780852</v>
+        <v>-1.917967047898223</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.705073533480772</v>
+        <v>-3.799000664761936</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9562785743152165</v>
+        <v>0.8999222955465176</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.29142324493986</v>
+        <v>-12.54318118773329</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.750654161532696</v>
+        <v>-1.851357338650066</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.539751007530958</v>
+        <v>-3.633678138812123</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.042420956238421</v>
+        <v>0.9860646774697228</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.06557809222045</v>
+        <v>-12.31733603501387</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.650737027408722</v>
+        <v>-1.751440204526092</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.497824331943795</v>
+        <v>-3.591751463224959</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.077156034626928</v>
+        <v>1.02079975585823</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.77930327989775</v>
+        <v>-12.03106122269118</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.535087957923585</v>
+        <v>-1.635791135040955</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.497824331943795</v>
+        <v>-3.591751463224959</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.078295179182987</v>
+        <v>1.021938900414288</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.83219856794204</v>
+        <v>-12.08395651073547</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.553612298979192</v>
+        <v>-1.654315476096563</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.492868985855349</v>
+        <v>-3.586796117136513</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.083902160998163</v>
+        <v>1.027545882229464</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.54828983701329</v>
+        <v>-11.80004777980672</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.434315102369056</v>
+        <v>-1.535018279486426</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.492868985855349</v>
+        <v>-3.586796117136513</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.089635865236799</v>
+        <v>1.0332795864681</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.4328689128752</v>
+        <v>-11.68462685566862</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.397883995107683</v>
+        <v>-1.498587172225053</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.377448061717253</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.149151157325791</v>
+        <v>1.092794878557092</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.16903204567113</v>
+        <v>-11.42078998846455</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.302232729538962</v>
+        <v>-1.402935906656333</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.377448061717253</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.139267676012884</v>
+        <v>1.082911397244185</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.90179024480273</v>
+        <v>-11.15354818759615</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.197170569690977</v>
+        <v>-1.297873746808347</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.377448061717253</v>
+        <v>-3.471375192998417</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.13743311551351</v>
+        <v>1.081076836744811</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.77848431632451</v>
+        <v>-11.03024225911793</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.148148513273151</v>
+        <v>-1.24885169039052</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.28803039058969</v>
+        <v>-3.381957521870854</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.190783403216587</v>
+        <v>1.134427124447888</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.75453077534855</v>
+        <v>-11.00628871814198</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.137898590737274</v>
+        <v>-1.238601767854643</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.264076849613732</v>
+        <v>-3.358003980894897</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.205824033947655</v>
+        <v>1.149467755178956</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.49047083702575</v>
+        <v>-10.74222877981918</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.045534931569907</v>
+        <v>-1.146238108687277</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.000016911290936</v>
+        <v>-3.093944042572101</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.350999680779581</v>
+        <v>1.294643402010882</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.783391213520916</v>
+        <v>-10.03514915631434</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.765490115828273</v>
+        <v>-0.8661932929456428</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.000016911290936</v>
+        <v>-3.093944042572101</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.34821264711928</v>
+        <v>1.291856368350581</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.743206915154726</v>
+        <v>-9.994964857948151</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7490727725939554</v>
+        <v>-0.8497759497113253</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.959832612924745</v>
+        <v>-3.05375974420591</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.372666850026836</v>
+        <v>1.316310571258137</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.663137119616922</v>
+        <v>-9.914895062410347</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7176780331580765</v>
+        <v>-0.8183812102754469</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.879762817386941</v>
+        <v>-2.973689948668106</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.420075548570275</v>
+        <v>1.363719269801576</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.429655897387324</v>
+        <v>-9.681413840180749</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6163611154283855</v>
+        <v>-0.7170642925457553</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.646281595157343</v>
+        <v>-2.740208726438507</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.568088710745886</v>
+        <v>1.511732431977188</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.24994736724345</v>
+        <v>-9.501705310036876</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5473699136837951</v>
+        <v>-0.6480730908011649</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.589110090994647</v>
+        <v>-2.683037222275811</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.599499402930545</v>
+        <v>1.543143124161846</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.117671893612563</v>
+        <v>-9.369429836405988</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4990922374844131</v>
+        <v>-0.599795414601783</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.45683461736376</v>
+        <v>-2.550761748644925</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.674232173856104</v>
+        <v>1.617875895087405</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.92707221893941</v>
+        <v>-9.178830161732835</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4200373069275152</v>
+        <v>-0.520740484044885</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.266234942690608</v>
+        <v>-2.360162073971772</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.791407039347632</v>
+        <v>1.735050760578933</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.678072420255829</v>
+        <v>-8.929830363049254</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.3075310462304239</v>
+        <v>-0.4082342233477938</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.266234942690608</v>
+        <v>-2.360162073971772</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.804313380571291</v>
+        <v>1.747957101802592</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.783662410028933</v>
+        <v>-9.035420352822358</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4777429717388841</v>
+        <v>-0.5784461488562544</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.371824932463712</v>
+        <v>-2.465752063744877</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.612983457108209</v>
+        <v>1.556627178339511</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.80239731214753</v>
+        <v>-9.054155254940955</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4366925907092369</v>
+        <v>-0.5373957678266068</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.371824932463712</v>
+        <v>-2.465752063744877</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.661527798985296</v>
+        <v>1.605171520216597</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.654457270739931</v>
+        <v>-8.906215213533356</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4973954968343648</v>
+        <v>-0.5980986739517347</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.351504016555154</v>
+        <v>-2.445431147836319</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.553841425842263</v>
+        <v>1.497485147073564</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.630228634350958</v>
+        <v>-8.881986577144383</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4964180285322537</v>
+        <v>-0.597121205649624</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.327275380166182</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.559664621422168</v>
+        <v>1.503308342653469</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.586680227580267</v>
+        <v>-8.838438170373692</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4859592779190702</v>
+        <v>-0.5866624550364405</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.327275380166182</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.552704009327075</v>
+        <v>1.496347730558376</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.344531834126409</v>
+        <v>-8.596289776919834</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3746375661563839</v>
+        <v>-0.4753407432737542</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.327275380166182</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.567166363708218</v>
+        <v>1.510810084939519</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.281302462358061</v>
+        <v>-8.533060405151486</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3548136969898499</v>
+        <v>-0.4555168741072202</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.327275380166182</v>
+        <v>-2.421202511447347</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.561698484167413</v>
+        <v>1.505342205398714</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.158011327540931</v>
+        <v>-8.409769270334357</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.3079991490524212</v>
+        <v>-0.4087023261697911</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.203984245349052</v>
+        <v>-2.297911376630216</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.633171259068268</v>
+        <v>1.576814980299569</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.136862128637489</v>
+        <v>-8.388620071430914</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2918384912537189</v>
+        <v>-0.3925416683710892</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.182835046445609</v>
+        <v>-2.276762177726773</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.653561756647659</v>
+        <v>1.59720547787896</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832483278809</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.893096686654045</v>
+        <v>-8.237663022565654</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1985516061132908</v>
+        <v>-0.3363781404779345</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.182835046445609</v>
+        <v>-2.276762177726773</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.64934246499471</v>
+        <v>1.592986186226011</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.629068619460785</v>
+        <v>-7.973634955372393</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.09081606531597064</v>
+        <v>-0.2286425996806143</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.980969647629655</v>
+        <v>-2.07489677891082</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.772586018204298</v>
+        <v>1.716229739435599</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.37921822551171</v>
+        <v>-7.723784561423319</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.001866167247360995</v>
+        <v>-0.1359603671172822</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.980969647629655</v>
+        <v>-2.07489677891082</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.765328093188</v>
+        <v>1.708971814419301</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.075650736507732</v>
+        <v>-7.42021707241934</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1268922863696016</v>
+        <v>-0.01093424799504206</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.980969647629655</v>
+        <v>-2.07489677891082</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.768927216708649</v>
+        <v>1.71257093793995</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.002170827655718</v>
+        <v>-7.346737163567326</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1696117559649606</v>
+        <v>0.03178522160031738</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.907489738777641</v>
+        <v>-2.001416870058805</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.826342668074411</v>
+        <v>1.769986389305712</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.777137827986895</v>
+        <v>-7.121704163898503</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2586454334487867</v>
+        <v>0.1208188990841434</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.682456739108818</v>
+        <v>-1.776383870389982</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.960382945492002</v>
+        <v>1.904026666723303</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.562503450350488</v>
+        <v>-6.907069786262096</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3491939855576667</v>
+        <v>0.2113674511930235</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.467822361472411</v>
+        <v>-1.561749492753576</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.093858373128163</v>
+        <v>2.037502094359464</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.295903093376136</v>
+        <v>-6.640469429287744</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4370283871312033</v>
+        <v>0.2992018527665601</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.467822361472411</v>
+        <v>-1.561749492753576</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.075052631911959</v>
+        <v>2.01869635314326</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.055472596571276</v>
+        <v>-6.400038932482884</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5349436624780246</v>
+        <v>0.3971171281133814</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.227391864667551</v>
+        <v>-1.321318995948715</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.221054006619752</v>
+        <v>2.164697727851054</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.812681788921831</v>
+        <v>-6.157248124833439</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6359892993726231</v>
+        <v>0.4981627650079798</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.227391864667551</v>
+        <v>-1.321318995948715</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.224983320454573</v>
+        <v>2.168627041685874</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.696741939296645</v>
+        <v>-6.041308275208253</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6830438231400371</v>
+        <v>0.5452172887753939</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.150570133651427</v>
+        <v>-1.244497264932591</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.271754942981587</v>
+        <v>2.215398664212888</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.454086350873482</v>
+        <v>-5.79865268678509</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7771041297292962</v>
+        <v>0.639277595364653</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.150570133651427</v>
+        <v>-1.244497264932591</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.26875301420158</v>
+        <v>2.212396735432882</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.234065552836471</v>
+        <v>-5.578631888748079</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8666914859547146</v>
+        <v>0.7288649515900714</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.009350288583447</v>
+        <v>-1.103277419864611</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.355063958252983</v>
+        <v>2.298707679484284</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.034816922931662</v>
+        <v>-5.37938325884327</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9622851207184615</v>
+        <v>0.8244585863538183</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.009350288583447</v>
+        <v>-1.103277419864611</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.370958141054806</v>
+        <v>2.314601862286107</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.875301819412292</v>
+        <v>-5.2198681553239</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.027237006566511</v>
+        <v>0.8894104722018681</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8498351850640767</v>
+        <v>-0.9437623163452412</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.46781304760673</v>
+        <v>2.411456768838031</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.730629674312555</v>
+        <v>-5.075196010224163</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.095193967167846</v>
+        <v>0.9573674328032027</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7051630399643394</v>
+        <v>-0.7990901712455039</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.564704437228012</v>
+        <v>2.508348158459313</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.790504501670247</v>
+        <v>-5.135070837581855</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.057281527626195</v>
+        <v>0.9194549932615517</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7650378673220315</v>
+        <v>-0.858964998603196</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.514817032214823</v>
+        <v>2.458460753446124</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.703705003891239</v>
+        <v>-5.048271339802847</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.114401820060364</v>
+        <v>0.9765752856957213</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7650378673220315</v>
+        <v>-0.858964998603196</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.537217525537389</v>
+        <v>2.48086124676869</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.604012389162227</v>
+        <v>-4.948578725073835</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.154351267325381</v>
+        <v>1.016524732960738</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6653452525930197</v>
+        <v>-0.7592723838741842</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.597105495748208</v>
+        <v>2.540749216979509</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.672382575486237</v>
+        <v>-5.016948911397845</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.138010115270479</v>
+        <v>1.000183580905836</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6560695535568047</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.613677837644639</v>
+        <v>2.55732155887594</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978365</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.550966145859761</v>
+        <v>-4.895532481771369</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.177013395752961</v>
+        <v>1.039186861388318</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6560695535568047</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.60411454627653</v>
+        <v>2.547758267507831</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.581959305188466</v>
+        <v>-4.926525641100074</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9893256970618658</v>
+        <v>0.8514991626972226</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6560695535568047</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.428824111316917</v>
+        <v>2.372467832548218</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.406485045395996</v>
+        <v>-4.751051381307605</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.064082632970641</v>
+        <v>0.9262560986059982</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6560695535568047</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.433391343308705</v>
+        <v>2.377035064540006</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.517421298037245</v>
+        <v>-4.861987633948853</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.019719605800939</v>
+        <v>0.8818930714362962</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6560695535568047</v>
+        <v>-0.7499966848379692</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.433402817195502</v>
+        <v>2.377046538426804</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.720447875580478</v>
+        <v>-5.065014211492087</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9416403600035517</v>
+        <v>0.8038138256389082</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8590961311000381</v>
+        <v>-0.9530232623812026</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.314718255889468</v>
+        <v>2.258361977120769</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734158</v>
+        <v>3.784340376734156</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.562522276645185</v>
+        <v>-4.907088612556794</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.014982986009801</v>
+        <v>0.877156451645158</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8590961311000381</v>
+        <v>-0.9530232623812026</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.3248906423216</v>
+        <v>2.268534363552901</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212294</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.710843530456314</v>
+        <v>-5.055409866367922</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9506007550592102</v>
+        <v>0.8127742206945667</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8590961311000381</v>
+        <v>-0.9530232623812026</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.319836912895461</v>
+        <v>2.263480634126762</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786042</v>
+        <v>3.75202392378604</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.712026615107375</v>
+        <v>-5.056592951018983</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9419032966433114</v>
+        <v>0.804076762278668</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8647391795665497</v>
+        <v>-0.9586663108477141</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.308226859260079</v>
+        <v>2.251870580491381</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273185</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.588898908113292</v>
+        <v>-4.9334652440249</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9917062524740463</v>
+        <v>0.8538797181094029</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8647391795665497</v>
+        <v>-0.9586663108477141</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.308778732293181</v>
+        <v>2.252422453524482</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.496088426662432</v>
+        <v>-4.84065476257404</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9581031369457558</v>
+        <v>0.8202766025811123</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.7719286981156903</v>
+        <v>-0.8658558293968548</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.293737713055062</v>
+        <v>2.237381434286363</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.447525374441402</v>
+        <v>-4.79209171035301</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9794018337587684</v>
+        <v>0.8415752993941252</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.7233656458946601</v>
+        <v>-0.8172927771758246</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.324749020312281</v>
+        <v>2.268392741543582</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.334854156205152</v>
+        <v>-4.67942049211676</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.019546029564992</v>
+        <v>0.8817194952003482</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.6106944276584099</v>
+        <v>-0.7046215589395743</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.387427459765754</v>
+        <v>2.331071180997055</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.836525561892339</v>
+        <v>3.551663147698817</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.885809789519812</v>
+        <v>2.706023743529244</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.334854156205152</v>
+        <v>-4.67942049211676</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.019546029564992</v>
+        <v>0.8817194952003482</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.6106944276584099</v>
+        <v>-0.7046215589395743</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.87887358650618</v>
+        <v>2.699087540515611</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240429.xlsx
+++ b/tame_output/ON/bt/strategyON_20240429.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-35.7%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.3%</t>
+          <t>-80.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.9%</t>
+          <t>117.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.5%</t>
+          <t>137.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-730.3%</t>
+          <t>-731.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.9%</t>
+          <t>-59.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-629.5%</t>
+          <t>-614.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-292.5%</t>
+          <t>-292.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>521.8%</t>
+          <t>-281.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-288.1%</t>
+          <t>-281.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-176.1%</t>
+          <t>-212.4%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7053466378184676</v>
+        <v>-0.7136758921499682</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.838833682885591</v>
+        <v>2.835501981152991</v>
       </c>
       <c r="F1845" t="n">
         <v>1.525689399526259</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9129124222100795</v>
+        <v>-0.9212416765415801</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.753632165248187</v>
+        <v>2.750300463515587</v>
       </c>
       <c r="F1846" t="n">
         <v>1.318123615134647</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.330666445756916</v>
+        <v>-1.338995700088417</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.584457447334516</v>
+        <v>2.581125745601915</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9003695915878102</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.552288379315034</v>
+        <v>-1.560617633646534</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.49567489051019</v>
+        <v>2.49234318877759</v>
       </c>
       <c r="F1848" t="n">
         <v>0.8628434579004411</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.760292437668111</v>
+        <v>-1.768621691999612</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.417365411722884</v>
+        <v>2.414033709990284</v>
       </c>
       <c r="F1849" t="n">
         <v>0.8628434579004411</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.971704858556086</v>
+        <v>-1.980034112887587</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.327881899705683</v>
+        <v>2.324550197973083</v>
       </c>
       <c r="F1850" t="n">
         <v>0.6514310370124661</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.310863236144608</v>
+        <v>-2.319192490476109</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.185302847976723</v>
+        <v>2.181971146244123</v>
       </c>
       <c r="F1851" t="n">
         <v>0.312272659423944</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.638880457872087</v>
+        <v>-2.647209712203588</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.0744342490245</v>
+        <v>2.0711025472919</v>
       </c>
       <c r="F1852" t="n">
         <v>-0.01574456230353516</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.132205329407265</v>
+        <v>-3.140534583738766</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.885203050818997</v>
+        <v>1.881871349086397</v>
       </c>
       <c r="F1853" t="n">
         <v>-0.1207306765431539</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.624590357431362</v>
+        <v>-3.632919611762863</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.689355431653091</v>
+        <v>1.68602372992049</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.6131157045672506</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-4.009770748361435</v>
+        <v>-4.018100002692935</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.533825814093925</v>
+        <v>1.530494112361324</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.6131157045672506</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.353453521588097</v>
+        <v>-4.361782775919598</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.398121828257876</v>
+        <v>1.394790126525276</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.7210217565944688</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.711103871826445</v>
+        <v>-4.719433126157946</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.251167746818795</v>
+        <v>1.247836045086194</v>
       </c>
       <c r="F1857" t="n">
         <v>-1.078672106832817</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-5.020337974822496</v>
+        <v>-5.028667229153997</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.129247032320634</v>
+        <v>1.125915330588033</v>
       </c>
       <c r="F1858" t="n">
         <v>-1.078672106832817</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.452143767972284</v>
+        <v>-5.460473022303784</v>
       </c>
       <c r="E1859" t="n">
-        <v>0.942857602528123</v>
+        <v>0.9395259007955228</v>
       </c>
       <c r="F1859" t="n">
         <v>-1.215089603274084</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.686837762104836</v>
+        <v>-5.695167016436336</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.8372647798771928</v>
+        <v>0.8339330781445926</v>
       </c>
       <c r="F1860" t="n">
         <v>-1.208753336044829</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-6.022500409335288</v>
+        <v>-6.030829663666789</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.701580312640977</v>
+        <v>0.6982486109083768</v>
       </c>
       <c r="F1861" t="n">
         <v>-1.208753336044829</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.386126654235602</v>
+        <v>-6.394455908567102</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.5626173749150931</v>
+        <v>0.5592856731824929</v>
       </c>
       <c r="F1862" t="n">
         <v>-1.306974972911954</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.751254036874348</v>
+        <v>-6.759583291205849</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.4158209368654258</v>
+        <v>0.4124892351328255</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.603285757210967</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-7.159842814055027</v>
+        <v>-7.168172068386527</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.2511469700079134</v>
+        <v>0.2478152682753136</v>
       </c>
       <c r="F1864" t="n">
         <v>-2.011874534391645</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.572825298196121</v>
+        <v>-7.581154552527621</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.08113940882293669</v>
+        <v>0.07780770709033646</v>
       </c>
       <c r="F1865" t="n">
         <v>-2.011874534391645</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.989217172483118</v>
+        <v>-7.997546426814618</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.08742329028298501</v>
+        <v>-0.09075499201558479</v>
       </c>
       <c r="F1866" t="n">
         <v>-2.011874534391645</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.365894183012962</v>
+        <v>-8.374223437344462</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.2278354038262433</v>
+        <v>-0.2311671055588436</v>
       </c>
       <c r="F1867" t="n">
         <v>-2.011874534391645</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.711769004997771</v>
+        <v>-8.720098259329271</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.370085767474472</v>
+        <v>-0.3734174692070718</v>
       </c>
       <c r="F1868" t="n">
         <v>-2.011874534391645</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.873911275460864</v>
+        <v>-8.882240529792364</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.4365377556047085</v>
+        <v>-0.4398694573373083</v>
       </c>
       <c r="F1869" t="n">
         <v>-2.011874534391645</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-9.170572617271063</v>
+        <v>-9.178901871602562</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.5514233163995796</v>
+        <v>-0.5547550181321794</v>
       </c>
       <c r="F1870" t="n">
         <v>-2.080617670125524</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.603921725381298</v>
+        <v>-9.612250979712798</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.7287892641780767</v>
+        <v>-0.7321209659106764</v>
       </c>
       <c r="F1871" t="n">
         <v>-2.080617670125524</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.986923114123929</v>
+        <v>-9.995252368455429</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.8820919209967131</v>
+        <v>-0.8854236227293129</v>
       </c>
       <c r="F1872" t="n">
         <v>-2.080617670125524</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.14432199433705</v>
+        <v>-10.15265124866855</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9424799571105313</v>
+        <v>-0.9458116588431316</v>
       </c>
       <c r="F1873" t="n">
         <v>-2.238016550338645</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.50385231684105</v>
+        <v>-10.51218157117255</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.080941782814082</v>
+        <v>-1.084273484546681</v>
       </c>
       <c r="F1874" t="n">
         <v>-2.238016550338645</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.83025234550606</v>
+        <v>-10.83858159983756</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.20358577432291</v>
+        <v>-1.206917476055509</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.564416579003658</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-11.04940131358026</v>
+        <v>-11.05773056791176</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.288203610930819</v>
+        <v>-1.29153531266342</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.783565547077855</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-11.04571038862385</v>
+        <v>-11.05403964295535</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.286727240948256</v>
+        <v>-1.290058942680855</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.783565547077855</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.24996856395371</v>
+        <v>-11.25829781828521</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.362917313961558</v>
+        <v>-1.366249015694159</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.911204491691844</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.46800633558489</v>
+        <v>-11.47633558991639</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.445649868129593</v>
+        <v>-1.448981569862193</v>
       </c>
       <c r="F1879" t="n">
         <v>-3.085975259787743</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.39453650391744</v>
+        <v>-11.40286575824894</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.400890233969193</v>
+        <v>-1.404221935701792</v>
       </c>
       <c r="F1880" t="n">
         <v>-3.012505428120295</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.56966092130399</v>
+        <v>-11.57799017563549</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.456384780176293</v>
+        <v>-1.459716481908893</v>
       </c>
       <c r="F1881" t="n">
         <v>-3.187629845506839</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.80411301531848</v>
+        <v>-11.81244226964998</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.557384782683685</v>
+        <v>-1.560716484416285</v>
       </c>
       <c r="F1882" t="n">
         <v>-3.187629845506839</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-12.09191685985571</v>
+        <v>-12.10024611418721</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.679178511272557</v>
+        <v>-1.682510213005157</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.475433690044077</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.32174130701954</v>
+        <v>-12.33007056135104</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.769992500299531</v>
+        <v>-1.77332420203213</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.638081227114237</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.5537702267558</v>
+        <v>-12.5620994810873</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.86011033956492</v>
+        <v>-1.863442041297521</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.70009392430266</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.50175471278699</v>
+        <v>-12.51008396711849</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.835313798290994</v>
+        <v>-1.838645500023595</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.70009392430266</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.64342655451111</v>
+        <v>-12.65175580884261</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.893457761879384</v>
+        <v>-1.896789463611984</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.70009392430266</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.74233329497038</v>
+        <v>-12.75066254930188</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.917967047898223</v>
+        <v>-1.921298749630822</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.799000664761936</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.54318118773329</v>
+        <v>-12.55151044206479</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.851357338650066</v>
+        <v>-1.854689040382665</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.633678138812123</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.31733603501387</v>
+        <v>-12.32566528934537</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.751440204526092</v>
+        <v>-1.754771906258692</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.591751463224959</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-12.03106122269118</v>
+        <v>-12.03939047702268</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.635791135040955</v>
+        <v>-1.639122836773555</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.591751463224959</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-12.08395651073547</v>
+        <v>-12.09228576506696</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.654315476096563</v>
+        <v>-1.657647177829162</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.586796117136513</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.80004777980672</v>
+        <v>-11.80837703413822</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.535018279486426</v>
+        <v>-1.538349981219026</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.586796117136513</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.68462685566862</v>
+        <v>-11.69295611000012</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.498587172225053</v>
+        <v>-1.501918873957653</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.471375192998417</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.42078998846455</v>
+        <v>-11.42911924279605</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.402935906656333</v>
+        <v>-1.406267608388932</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.471375192998417</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-11.15354818759615</v>
+        <v>-11.16187744192765</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.297873746808347</v>
+        <v>-1.301205448540947</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.471375192998417</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-11.03024225911793</v>
+        <v>-11.03857151344943</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.24885169039052</v>
+        <v>-1.252183392123121</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.381957521870854</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-11.00628871814198</v>
+        <v>-11.01461797247348</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.238601767854643</v>
+        <v>-1.241933469587244</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.358003980894897</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.74222877981918</v>
+        <v>-10.75055803415068</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.146238108687277</v>
+        <v>-1.149569810419877</v>
       </c>
       <c r="F1899" t="n">
         <v>-3.093944042572101</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-10.03514915631434</v>
+        <v>-10.04347841064584</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.8661932929456428</v>
+        <v>-0.8695249946782431</v>
       </c>
       <c r="F1900" t="n">
         <v>-3.093944042572101</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.994964857948151</v>
+        <v>-10.00329411227965</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.8497759497113253</v>
+        <v>-0.8531076514439255</v>
       </c>
       <c r="F1901" t="n">
         <v>-3.05375974420591</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.914895062410347</v>
+        <v>-9.923224316741846</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.8183812102754469</v>
+        <v>-0.8217129120080466</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.973689948668106</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.681413840180749</v>
+        <v>-9.689743094512249</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.7170642925457553</v>
+        <v>-0.7203959942783551</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.740208726438507</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.501705310036876</v>
+        <v>-9.510034564368375</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.6480730908011649</v>
+        <v>-0.6514047925337652</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.683037222275811</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.369429836405988</v>
+        <v>-9.377759090737488</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.599795414601783</v>
+        <v>-0.6031271163343832</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.550761748644925</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-9.178830161732835</v>
+        <v>-9.187159416064334</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.520740484044885</v>
+        <v>-0.5240721857774848</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.360162073971772</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.929830363049254</v>
+        <v>-8.938159617380753</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.4082342233477938</v>
+        <v>-0.4115659250803936</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.360162073971772</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-9.035420352822358</v>
+        <v>-9.043749607153858</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5784461488562544</v>
+        <v>-0.5817778505888542</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.465752063744877</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-9.054155254940955</v>
+        <v>-9.062484509272455</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.5373957678266068</v>
+        <v>-0.5407274695592066</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.465752063744877</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.906215213533356</v>
+        <v>-8.914544467864856</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.5980986739517347</v>
+        <v>-0.6014303756843344</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.445431147836319</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.881986577144383</v>
+        <v>-8.890315831475883</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.597121205649624</v>
+        <v>-0.6004529073822238</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.421202511447347</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.838438170373692</v>
+        <v>-8.846767424705192</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5866624550364405</v>
+        <v>-0.5899941567690403</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.421202511447347</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.596289776919834</v>
+        <v>-8.604619031251334</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.4753407432737542</v>
+        <v>-0.478672445006354</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.421202511447347</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.533060405151486</v>
+        <v>-8.541389659482986</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.4555168741072202</v>
+        <v>-0.45884857583982</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.421202511447347</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.409769270334357</v>
+        <v>-8.418098524665856</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.4087023261697911</v>
+        <v>-0.4120340279023913</v>
       </c>
       <c r="F1915" t="n">
         <v>-2.297911376630216</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.388620071430914</v>
+        <v>-8.396949325762414</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3925416683710892</v>
+        <v>-0.3958733701036889</v>
       </c>
       <c r="F1916" t="n">
         <v>-2.276762177726773</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-8.237663022565654</v>
+        <v>-8.153183883778969</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.3363781404779345</v>
+        <v>-0.30258648496326</v>
       </c>
       <c r="F1917" t="n">
         <v>-2.276762177726773</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.973634955372393</v>
+        <v>-7.889155816585708</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.2286425996806143</v>
+        <v>-0.1948509441659398</v>
       </c>
       <c r="F1918" t="n">
         <v>-2.07489677891082</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.723784561423319</v>
+        <v>-7.639305422636633</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.1359603671172822</v>
+        <v>-0.1021687116026082</v>
       </c>
       <c r="F1919" t="n">
         <v>-2.07489677891082</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.42021707241934</v>
+        <v>-7.335737933632655</v>
       </c>
       <c r="E1920" t="n">
-        <v>-0.01093424799504206</v>
+        <v>0.02285740751963239</v>
       </c>
       <c r="F1920" t="n">
         <v>-2.07489677891082</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.346737163567326</v>
+        <v>-7.262258024780641</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.03178522160031738</v>
+        <v>0.06557687711499138</v>
       </c>
       <c r="F1921" t="n">
         <v>-2.001416870058805</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-7.121704163898503</v>
+        <v>-7.037225025111818</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.1208188990841434</v>
+        <v>0.1546105545988175</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.776383870389982</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.907069786262096</v>
+        <v>-6.822590647475411</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.2113674511930235</v>
+        <v>0.2451591067076975</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.561749492753576</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.640469429287744</v>
+        <v>-6.555990290501059</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.2992018527665601</v>
+        <v>0.3329935082812341</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.561749492753576</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.400038932482884</v>
+        <v>-6.315559793696199</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.3971171281133814</v>
+        <v>0.4309087836280554</v>
       </c>
       <c r="F1925" t="n">
         <v>-1.321318995948715</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.157248124833439</v>
+        <v>-6.072768986046754</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.4981627650079798</v>
+        <v>0.5319544205226538</v>
       </c>
       <c r="F1926" t="n">
         <v>-1.321318995948715</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.041308275208253</v>
+        <v>-5.956829136421568</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5452172887753939</v>
+        <v>0.5790089442900679</v>
       </c>
       <c r="F1927" t="n">
         <v>-1.244497264932591</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.79865268678509</v>
+        <v>-5.714173547998405</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.639277595364653</v>
+        <v>0.673069250879327</v>
       </c>
       <c r="F1928" t="n">
         <v>-1.244497264932591</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.578631888748079</v>
+        <v>-5.494152749961394</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7288649515900714</v>
+        <v>0.7626566071047454</v>
       </c>
       <c r="F1929" t="n">
         <v>-1.103277419864611</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.37938325884327</v>
+        <v>-5.294904120056585</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8244585863538183</v>
+        <v>0.8582502418684923</v>
       </c>
       <c r="F1930" t="n">
         <v>-1.103277419864611</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.2198681553239</v>
+        <v>-5.135389016537215</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8894104722018681</v>
+        <v>0.9232021277165421</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.9437623163452412</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.075196010224163</v>
+        <v>-4.990716871437478</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9573674328032027</v>
+        <v>0.9911590883178769</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.7990901712455039</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.135070837581855</v>
+        <v>-5.05059169879517</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9194549932615517</v>
+        <v>0.9532466487762257</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.858964998603196</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.048271339802847</v>
+        <v>-4.963792201016162</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9765752856957213</v>
+        <v>1.010366941210395</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.858964998603196</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.948578725073835</v>
+        <v>-4.86409958628715</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.016524732960738</v>
+        <v>1.050316388475412</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.7592723838741842</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.016948911397845</v>
+        <v>-4.93246977261116</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.000183580905836</v>
+        <v>1.03397523642051</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.7499966848379692</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.895532481771369</v>
+        <v>-4.811053342984684</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.039186861388318</v>
+        <v>1.072978516902992</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.7499966848379692</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.926525641100074</v>
+        <v>-4.842046502313389</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8514991626972226</v>
+        <v>0.8852908182118966</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.7499966848379692</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.751051381307605</v>
+        <v>-4.666572242520919</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9262560986059982</v>
+        <v>0.9600477541206722</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.7499966848379692</v>
@@ -46171,10 +46171,10 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.861987633948853</v>
+        <v>-4.777508495162168</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8818930714362962</v>
+        <v>0.9156847269509703</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.7499966848379692</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.065014211492087</v>
+        <v>-4.980535072705401</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8038138256389082</v>
+        <v>0.8376054811535825</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.9530232623812026</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.907088612556794</v>
+        <v>-4.822609473770108</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.877156451645158</v>
+        <v>0.910948107159832</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.9530232623812026</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.055409866367922</v>
+        <v>-4.970930727581237</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8127742206945667</v>
+        <v>0.846565876209241</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.9530232623812026</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.056592951018983</v>
+        <v>-4.972113812232298</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.804076762278668</v>
+        <v>0.8378684177933422</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.9586663108477141</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.9334652440249</v>
+        <v>-4.848986105238215</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8538797181094029</v>
+        <v>0.8876713736240771</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.9586663108477141</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.84065476257404</v>
+        <v>-4.756175623787355</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8202766025811123</v>
+        <v>0.8540682580957866</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.8658558293968548</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.79209171035301</v>
+        <v>-4.707612571566325</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8415752993941252</v>
+        <v>0.8753669549087992</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.8172927771758246</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.67942049211676</v>
+        <v>-4.594941353330075</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8817194952003482</v>
+        <v>0.9155111507150224</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.7046215589395743</v>
@@ -46375,19 +46375,19 @@
         <v>3.551663147698817</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.706023743529244</v>
+        <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.67942049211676</v>
+        <v>-4.529179791827533</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8817194952003482</v>
+        <v>0.9473070711467062</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.7046215589395743</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.699087540515611</v>
+        <v>2.336562476827722</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240429.xlsx
+++ b/tame_output/ON/bt/strategyON_20240429.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>45.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-32.8%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.2%</t>
+          <t>116.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.6%</t>
+          <t>137.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-731.1%</t>
+          <t>-716.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-59.0%</t>
+          <t>-58.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>439.9%</t>
+          <t>445.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-614.5%</t>
+          <t>-616.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-292.8%</t>
+          <t>-287.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-281.6%</t>
+          <t>-201.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-281.5%</t>
+          <t>-279.2%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-344.9%</t>
+          <t>-340.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-167.8%</t>
+          <t>-166.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-294.5%</t>
+          <t>-290.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-207.3%</t>
+          <t>-205.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-212.4%</t>
+          <t>-206.9%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7136758921499682</v>
+        <v>-0.6091471528189167</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.835501981152991</v>
+        <v>2.877313476885412</v>
       </c>
       <c r="F1845" t="n">
         <v>1.525689399526259</v>
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9212416765415801</v>
+        <v>-0.7775026012156842</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.750300463515587</v>
+        <v>2.807796093645945</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.318123615134647</v>
+        <v>1.357333951129492</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.910027727526755</v>
+        <v>3.933553929123661</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.338995700088417</v>
+        <v>-1.195256624762521</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.581125745601915</v>
+        <v>2.638621375732273</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9003695915878102</v>
+        <v>0.9395799275826547</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.657302204903716</v>
+        <v>3.680828406500622</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.560617633646534</v>
+        <v>-1.416878558320639</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.49234318877759</v>
+        <v>2.549838818907948</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8628434579004411</v>
+        <v>0.9020537938952857</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.634652741290216</v>
+        <v>3.658178942887123</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.768621691999612</v>
+        <v>-1.624882616673716</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.414033709990284</v>
+        <v>2.471529340120643</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8628434579004411</v>
+        <v>0.9020537938952857</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.639544885844141</v>
+        <v>3.663071087441048</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.980034112887587</v>
+        <v>-1.836295037561691</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.324550197973083</v>
+        <v>2.382045828103441</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6514310370124661</v>
+        <v>0.6906413730073107</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.507778889649344</v>
+        <v>3.531305091246251</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.319192490476109</v>
+        <v>-2.175453415150213</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.181971146244123</v>
+        <v>2.239466776374481</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.312272659423944</v>
+        <v>0.3514829954187886</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.29736816240268</v>
+        <v>3.320894363999587</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.647209712203588</v>
+        <v>-2.503470636877692</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.0711025472919</v>
+        <v>2.128598177422258</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.01574456230353516</v>
+        <v>0.02346577369130942</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.120896119104961</v>
+        <v>3.144422320701868</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.140534583738766</v>
+        <v>-2.99679550841287</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.881871349086397</v>
+        <v>1.939366979216755</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.1207306765431539</v>
+        <v>-0.08152034054830931</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.066003200969758</v>
+        <v>3.089529402566665</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.632919611762863</v>
+        <v>-3.489180536436967</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.68602372992049</v>
+        <v>1.743519360050849</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.573905368572406</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.771678576199033</v>
+        <v>2.795204777795939</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-4.018100002692935</v>
+        <v>-3.874360927367039</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.530494112361324</v>
+        <v>1.587989742491683</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.6131157045672506</v>
+        <v>-0.573905368572406</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.770221115011896</v>
+        <v>2.793747316608802</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.361782775919598</v>
+        <v>-4.218043700593702</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.394790126525276</v>
+        <v>1.452285756655634</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.7210217565944688</v>
+        <v>-0.6818114205996242</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.707246607250181</v>
+        <v>2.730772808847088</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.719433126157946</v>
+        <v>-4.57569405083205</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.247836045086194</v>
+        <v>1.305331675216553</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.078672106832817</v>
+        <v>-1.039461770837972</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.48876245576343</v>
+        <v>2.512288657360337</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-5.028667229153997</v>
+        <v>-4.884928153828101</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.125915330588033</v>
+        <v>1.183410960718392</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.078672106832817</v>
+        <v>-1.039461770837972</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.49053538246369</v>
+        <v>2.514061584060596</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.460473022303784</v>
+        <v>-5.316733946977888</v>
       </c>
       <c r="E1859" t="n">
-        <v>0.9395259007955228</v>
+        <v>0.9970215309258812</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.215089603274084</v>
+        <v>-1.175879267279239</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.395017772066334</v>
+        <v>2.41854397366324</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.695167016436336</v>
+        <v>-5.551427941110441</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.8339330781445926</v>
+        <v>0.891428708274951</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.169543000049984</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.387104307405978</v>
+        <v>2.410630509002885</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-6.030829663666789</v>
+        <v>-5.887090588340893</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.6982486109083768</v>
+        <v>0.7557442410387352</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.208753336044829</v>
+        <v>-1.169543000049984</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.385684899061943</v>
+        <v>2.40921110065885</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.394455908567102</v>
+        <v>-6.250716833241206</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.5592856731824929</v>
+        <v>0.6167813033128513</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.306974972911954</v>
+        <v>-1.26776463691711</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.333239477175909</v>
+        <v>2.356765678772816</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.759583291205849</v>
+        <v>-6.615844215879953</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.4124892351328255</v>
+        <v>0.4699848652631839</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.603285757210967</v>
+        <v>-1.564075421216122</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.154707521602333</v>
+        <v>2.17823372319924</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-7.168172068386527</v>
+        <v>-7.024432993060632</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.2478152682753136</v>
+        <v>0.3053108984056716</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.972664198396801</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.908315799308685</v>
+        <v>1.931842000905592</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.581154552527621</v>
+        <v>-7.437415477201726</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.07780770709033646</v>
+        <v>0.1353033372206944</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.972664198396801</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.903501231780145</v>
+        <v>1.927027433377052</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.997546426814618</v>
+        <v>-7.853807351488723</v>
       </c>
       <c r="E1866" t="n">
-        <v>-0.09075499201558479</v>
+        <v>-0.03325936188522682</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.972664198396801</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.901495282389023</v>
+        <v>1.92502148398593</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.374223437344462</v>
+        <v>-8.230484362018567</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.2311671055588436</v>
+        <v>-0.1736714754284856</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.972664198396801</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.911753973057702</v>
+        <v>1.935280174654609</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.720098259329271</v>
+        <v>-8.576359184003376</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.3734174692070718</v>
+        <v>-0.3159218390767138</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.972664198396801</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.907853538203397</v>
+        <v>1.931379739800303</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.882240529792364</v>
+        <v>-8.738501454466469</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.4398694573373083</v>
+        <v>-0.3823738272069503</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.011874534391645</v>
+        <v>-1.972664198396801</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.906258458258398</v>
+        <v>1.929784659855304</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-9.178901871602562</v>
+        <v>-9.035162796276667</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.5547550181321794</v>
+        <v>-0.4972593880018215</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.04140733413068</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.868791552747279</v>
+        <v>1.892317754344186</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.612250979712798</v>
+        <v>-9.468511904386903</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.7321209659106764</v>
+        <v>-0.6746253357803185</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.04140733413068</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.864765248212876</v>
+        <v>1.888291449809782</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.995252368455429</v>
+        <v>-9.851513293129534</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.8854236227293129</v>
+        <v>-0.8279279925989549</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.080617670125524</v>
+        <v>-2.04140733413068</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.864663146891292</v>
+        <v>1.888189348488198</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.15265124866855</v>
+        <v>-10.00891217334265</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9458116588431316</v>
+        <v>-0.8883160287127736</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.198806214343801</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.772795334734849</v>
+        <v>1.796321536331756</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.51218157117255</v>
+        <v>-10.36844249584666</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.084273484546681</v>
+        <v>-1.026777854416324</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.238016550338645</v>
+        <v>-2.198806214343801</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.778145638032899</v>
+        <v>1.801671839629806</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.83858159983756</v>
+        <v>-10.69484252451167</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.206917476055509</v>
+        <v>-1.149421845925151</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.564416579003658</v>
+        <v>-2.525206243008814</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.590221640791069</v>
+        <v>1.613747842387976</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-11.05773056791176</v>
+        <v>-10.91399149258587</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.29153531266342</v>
+        <v>-1.234039682533062</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.744355211083011</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.461774010568319</v>
+        <v>1.485300212165226</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-11.05403964295535</v>
+        <v>-10.91030056762946</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.290058942680855</v>
+        <v>-1.232563312550497</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.783565547077855</v>
+        <v>-2.744355211083011</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.461774010568319</v>
+        <v>1.485300212165226</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.25829781828521</v>
+        <v>-11.11455874295932</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.366249015694159</v>
+        <v>-1.308753385563801</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.911204491691844</v>
+        <v>-2.871994155697</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.390703840918569</v>
+        <v>1.414230042515475</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.47633558991639</v>
+        <v>-11.3325965145905</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.448981569862193</v>
+        <v>-1.391485939731835</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.085975259787743</v>
+        <v>-3.046764923792899</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.290323934545465</v>
+        <v>1.313850136142372</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.40286575824894</v>
+        <v>-11.25912668292305</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.404221935701792</v>
+        <v>-1.346726305571434</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.012505428120295</v>
+        <v>-2.973295092125451</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.349777535039355</v>
+        <v>1.373303736636262</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.57799017563549</v>
+        <v>-11.43425110030959</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.459716481908893</v>
+        <v>-1.402220851778536</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.148419509511994</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.259258105354946</v>
+        <v>1.282784306951853</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.81244226964998</v>
+        <v>-11.66870319432408</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.560716484416285</v>
+        <v>-1.503220854285927</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.187629845506839</v>
+        <v>-3.148419509511994</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.25203894045335</v>
+        <v>1.275565142050257</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-12.10024611418721</v>
+        <v>-11.95650703886132</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.682510213005157</v>
+        <v>-1.625014582874799</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.475433690044077</v>
+        <v>-3.436223354049233</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.072684442957031</v>
+        <v>1.096210644553937</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.33007056135104</v>
+        <v>-12.18633148602514</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.77332420203213</v>
+        <v>-1.715828571901772</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.638081227114237</v>
+        <v>-3.598870891119393</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9762117105534909</v>
+        <v>0.9997379121503975</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.5620994810873</v>
+        <v>-12.41836040576141</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.863442041297521</v>
+        <v>-1.805946411167163</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.660883588307816</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9416978208695514</v>
+        <v>0.9652240224664581</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.51008396711849</v>
+        <v>-12.48421991258823</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.838645500023595</v>
+        <v>-1.828299878211491</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.660883588307816</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9456881565559523</v>
+        <v>0.9692143581528589</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.65175580884261</v>
+        <v>-12.62589175431235</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.896789463611984</v>
+        <v>-1.886443841799881</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.70009392430266</v>
+        <v>-3.660883588307816</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9442129296572106</v>
+        <v>0.9677391312541173</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.75066254930188</v>
+        <v>-12.72479849477163</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.921298749630822</v>
+        <v>-1.910953127818719</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.799000664761936</v>
+        <v>-3.759790328767092</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8999222955465176</v>
+        <v>0.9234484971434243</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.55151044206479</v>
+        <v>-12.52564638753453</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.854689040382665</v>
+        <v>-1.844343418570562</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.633678138812123</v>
+        <v>-3.594467802817279</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9860646774697228</v>
+        <v>1.009590879066629</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.32566528934537</v>
+        <v>-12.29980123481512</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.754771906258692</v>
+        <v>-1.74442628444659</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.552541127230115</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.02079975585823</v>
+        <v>1.044325957455136</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-12.03939047702268</v>
+        <v>-12.01352642249242</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.639122836773555</v>
+        <v>-1.628777214961453</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.591751463224959</v>
+        <v>-3.552541127230115</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.021938900414288</v>
+        <v>1.045465102011195</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-12.09228576506696</v>
+        <v>-12.06642171053671</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.657647177829162</v>
+        <v>-1.64730155601706</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.547585781141669</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.027545882229464</v>
+        <v>1.05107208382637</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.80837703413822</v>
+        <v>-11.78251297960796</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.538349981219026</v>
+        <v>-1.528004359406924</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.586796117136513</v>
+        <v>-3.547585781141669</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.0332795864681</v>
+        <v>1.056805788065007</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.69295611000012</v>
+        <v>-11.66709205546986</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.501918873957653</v>
+        <v>-1.49157325214555</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.432164857003573</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.092794878557092</v>
+        <v>1.116321080153999</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.42911924279605</v>
+        <v>-11.40325518826579</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.406267608388932</v>
+        <v>-1.39592198657683</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.432164857003573</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.082911397244185</v>
+        <v>1.106437598841091</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-11.16187744192765</v>
+        <v>-11.1360133873974</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.301205448540947</v>
+        <v>-1.290859826728844</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.471375192998417</v>
+        <v>-3.432164857003573</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.081076836744811</v>
+        <v>1.104603038341718</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-11.03857151344943</v>
+        <v>-11.01270745891918</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.252183392123121</v>
+        <v>-1.241837770311017</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.381957521870854</v>
+        <v>-3.34274718587601</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.134427124447888</v>
+        <v>1.157953326044795</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-11.01461797247348</v>
+        <v>-10.98875391794322</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.241933469587244</v>
+        <v>-1.231587847775141</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.358003980894897</v>
+        <v>-3.318793644900053</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.149467755178956</v>
+        <v>1.172993956775863</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.75055803415068</v>
+        <v>-10.72469397962042</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.149569810419877</v>
+        <v>-1.139224188607774</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.054733706577256</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.294643402010882</v>
+        <v>1.318169603607788</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-10.04347841064584</v>
+        <v>-10.01761435611559</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.8695249946782431</v>
+        <v>-0.8591793728661408</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.093944042572101</v>
+        <v>-3.054733706577256</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.291856368350581</v>
+        <v>1.315382569947487</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-10.00329411227965</v>
+        <v>-9.977430057749395</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.8531076514439255</v>
+        <v>-0.8427620296318228</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.05375974420591</v>
+        <v>-3.014549408211066</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.316310571258137</v>
+        <v>1.339836772855043</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.923224316741846</v>
+        <v>-9.89736026221159</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.8217129120080466</v>
+        <v>-0.8113672901959443</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.973689948668106</v>
+        <v>-2.934479612673262</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.363719269801576</v>
+        <v>1.387245471398483</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.689743094512249</v>
+        <v>-9.663879039981992</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.7203959942783551</v>
+        <v>-0.7100503724662528</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.740208726438507</v>
+        <v>-2.700998390443663</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.511732431977188</v>
+        <v>1.535258633574094</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.510034564368375</v>
+        <v>-9.484170509838119</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.6514047925337652</v>
+        <v>-0.6410591707216624</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.683037222275811</v>
+        <v>-2.643826886280967</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.543143124161846</v>
+        <v>1.566669325758753</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860423</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.377759090737488</v>
+        <v>-9.351895036207232</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.6031271163343832</v>
+        <v>-0.5927814945222805</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.550761748644925</v>
+        <v>-2.511551412650081</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.617875895087405</v>
+        <v>1.641402096684311</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-9.187159416064334</v>
+        <v>-9.161295361534078</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.5240721857774848</v>
+        <v>-0.5137265639653825</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.320951737976928</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.735050760578933</v>
+        <v>1.75857696217584</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.938159617380753</v>
+        <v>-8.912295562850497</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.4115659250803936</v>
+        <v>-0.4012203032682913</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.360162073971772</v>
+        <v>-2.320951737976928</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.747957101802592</v>
+        <v>1.771483303399499</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-9.043749607153858</v>
+        <v>-9.017885552623602</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.5817778505888542</v>
+        <v>-0.5714322287767519</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.426541727750033</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.556627178339511</v>
+        <v>1.580153379936417</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-9.062484509272455</v>
+        <v>-9.036620454742199</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.5407274695592066</v>
+        <v>-0.5303818477471043</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.465752063744877</v>
+        <v>-2.426541727750033</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.605171520216597</v>
+        <v>1.628697721813503</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.914544467864856</v>
+        <v>-8.888680413334599</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.6014303756843344</v>
+        <v>-0.5910847538722321</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.445431147836319</v>
+        <v>-2.406220811841475</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.497485147073564</v>
+        <v>1.521011348670471</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.890315831475883</v>
+        <v>-8.864451776945627</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.6004529073822238</v>
+        <v>-0.590107285570121</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.381992175452503</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.503308342653469</v>
+        <v>1.526834544250376</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568104</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.846767424705192</v>
+        <v>-8.820903370174936</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.5899941567690403</v>
+        <v>-0.579648534956938</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.381992175452503</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.496347730558376</v>
+        <v>1.519873932155283</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963415</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.604619031251334</v>
+        <v>-8.578754976721077</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.478672445006354</v>
+        <v>-0.4683268231942517</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.381992175452503</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.510810084939519</v>
+        <v>1.534336286536426</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192813</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.541389659482986</v>
+        <v>-8.51552560495273</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.45884857583982</v>
+        <v>-0.4485029540277177</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.421202511447347</v>
+        <v>-2.381992175452503</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.505342205398714</v>
+        <v>1.528868406995621</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.418098524665856</v>
+        <v>-8.3922344701356</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.4120340279023913</v>
+        <v>-0.4016884060902886</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.297911376630216</v>
+        <v>-2.258701040635372</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.576814980299569</v>
+        <v>1.600341181896476</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.396949325762414</v>
+        <v>-8.371085271232158</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.3958733701036889</v>
+        <v>-0.3855277482915866</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.276762177726773</v>
+        <v>-2.237551841731929</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.59720547787896</v>
+        <v>1.620731679475867</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-8.153183883778969</v>
+        <v>-8.127319829248712</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.30258648496326</v>
+        <v>-0.2922408631511577</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.276762177726773</v>
+        <v>-2.237551841731929</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.592986186226011</v>
+        <v>1.616512387822918</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.889155816585708</v>
+        <v>-7.863291762055452</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.1948509441659398</v>
+        <v>-0.1845053223538375</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.07489677891082</v>
+        <v>-2.035686442915976</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.716229739435599</v>
+        <v>1.739755941032506</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.639305422636633</v>
+        <v>-7.613441368106377</v>
       </c>
       <c r="E1919" t="n">
-        <v>-0.1021687116026082</v>
+        <v>-0.09182308979050546</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.07489677891082</v>
+        <v>-2.035686442915976</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.708971814419301</v>
+        <v>1.732498016016208</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.335737933632655</v>
+        <v>-7.309873879102398</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.02285740751963239</v>
+        <v>0.03320302933173469</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.07489677891082</v>
+        <v>-2.035686442915976</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.71257093793995</v>
+        <v>1.736097139536857</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.262258024780641</v>
+        <v>-7.236393970250385</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.06557687711499138</v>
+        <v>0.07592249892709413</v>
       </c>
       <c r="F1921" t="n">
-        <v>-2.001416870058805</v>
+        <v>-1.962206534063961</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.769986389305712</v>
+        <v>1.793512590902619</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-7.037225025111818</v>
+        <v>-7.011360970581562</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.1546105545988175</v>
+        <v>0.1649561764109202</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.776383870389982</v>
+        <v>-1.737173534395138</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.904026666723303</v>
+        <v>1.927552868320209</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.822590647475411</v>
+        <v>-6.796726592945155</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.2451591067076975</v>
+        <v>0.2555047285198002</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.561749492753576</v>
+        <v>-1.522539156758731</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.037502094359464</v>
+        <v>2.061028295956371</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.555990290501059</v>
+        <v>-6.530126235970803</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3329935082812341</v>
+        <v>0.3433391300933364</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.561749492753576</v>
+        <v>-1.522539156758731</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.01869635314326</v>
+        <v>2.042222554740166</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.315559793696199</v>
+        <v>-6.289695739165943</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4309087836280554</v>
+        <v>0.4412544054401581</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.321318995948715</v>
+        <v>-1.282108659953871</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.164697727851054</v>
+        <v>2.18822392944796</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.072768986046754</v>
+        <v>-6.046904931516497</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5319544205226538</v>
+        <v>0.5423000423347561</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.321318995948715</v>
+        <v>-1.282108659953871</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.168627041685874</v>
+        <v>2.19215324328278</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349965</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.956829136421568</v>
+        <v>-5.930965081891312</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5790089442900679</v>
+        <v>0.5893545661021706</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.244497264932591</v>
+        <v>-1.205286928937747</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.215398664212888</v>
+        <v>2.238924865809794</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.714173547998405</v>
+        <v>-5.688309493468148</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.673069250879327</v>
+        <v>0.6834148726914293</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.244497264932591</v>
+        <v>-1.205286928937747</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.212396735432882</v>
+        <v>2.235922937029788</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145934</v>
+        <v>3.818665376145938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.494152749961394</v>
+        <v>-5.468288695431138</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7626566071047454</v>
+        <v>0.7730022289168477</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.103277419864611</v>
+        <v>-1.064067083869767</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.298707679484284</v>
+        <v>2.32223388108119</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009946</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.294904120056585</v>
+        <v>-5.269040065526329</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8582502418684923</v>
+        <v>0.8685958636805946</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.103277419864611</v>
+        <v>-1.064067083869767</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.314601862286107</v>
+        <v>2.338128063883014</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.135389016537215</v>
+        <v>-5.109524962006959</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9232021277165421</v>
+        <v>0.9335477495286444</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.9437623163452412</v>
+        <v>-0.9045519803503971</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.411456768838031</v>
+        <v>2.434982970434937</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.990716871437478</v>
+        <v>-4.964852816907221</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9911590883178769</v>
+        <v>1.001504710129979</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7990901712455039</v>
+        <v>-0.7598798352506597</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.508348158459313</v>
+        <v>2.53187436005622</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.05059169879517</v>
+        <v>-5.024727644264914</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9532466487762257</v>
+        <v>0.9635922705883284</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.858964998603196</v>
+        <v>-0.8197546626083518</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.458460753446124</v>
+        <v>2.48198695504303</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.963792201016162</v>
+        <v>-4.937928146485906</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.010366941210395</v>
+        <v>1.020712563022498</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.858964998603196</v>
+        <v>-0.8197546626083518</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.48086124676869</v>
+        <v>2.504387448365597</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.996312647304019</v>
+        <v>3.02149508761399</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.86409958628715</v>
+        <v>-4.838235531756894</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.050316388475412</v>
+        <v>1.085844450597485</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.7592723838741842</v>
+        <v>-0.72006204787934</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.540749216979509</v>
+        <v>2.589457858886386</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.007319569778721</v>
+        <v>3.032502010088692</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.93246977261116</v>
+        <v>-4.906605718080904</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.03397523642051</v>
+        <v>1.069503298542583</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7107863488431251</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.55732155887594</v>
+        <v>2.606030200782818</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.997756278410613</v>
+        <v>3.022938718720583</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.811053342984684</v>
+        <v>-4.785189288454427</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.072978516902992</v>
+        <v>1.108506579025065</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7107863488431251</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.547758267507831</v>
+        <v>2.596466909414709</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887698</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>2.84764828376097</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.842046502313389</v>
+        <v>-4.816182447783133</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8852908182118966</v>
+        <v>0.9208188803339699</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7107863488431251</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.372467832548218</v>
+        <v>2.421176474455096</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>2.852215515752758</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.666572242520919</v>
+        <v>-4.640708187990663</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9600477541206722</v>
+        <v>0.9955758162427455</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7107863488431251</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.377035064540006</v>
+        <v>2.425743706446883</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.827044549329585</v>
+        <v>2.852226989639556</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.777508495162168</v>
+        <v>-4.751644440631912</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9156847269509703</v>
+        <v>0.9512127890730435</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.7499966848379692</v>
+        <v>-0.7107863488431251</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.377046538426804</v>
+        <v>2.425755180333681</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.83017593454949</v>
+        <v>2.855358374859461</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.980535072705401</v>
+        <v>-4.954671018175145</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8376054811535825</v>
+        <v>0.8731335432756557</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.9530232623812026</v>
+        <v>-0.9138129263863585</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.258361977120769</v>
+        <v>2.307070619027646</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734156</v>
+        <v>3.78434037673416</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.840348320981623</v>
+        <v>2.865530761291593</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.822609473770108</v>
+        <v>-4.796745419239852</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.910948107159832</v>
+        <v>0.9464761692819053</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.9530232623812026</v>
+        <v>-0.9138129263863585</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.268534363552901</v>
+        <v>2.317243005459779</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212296</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.835294591555483</v>
+        <v>2.860477031865454</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.970930727581237</v>
+        <v>-4.945066673050981</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.846565876209241</v>
+        <v>0.8820939383313142</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.9530232623812026</v>
+        <v>-0.9138129263863585</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.263480634126762</v>
+        <v>2.312189276033639</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202392378604</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.827070367000009</v>
+        <v>2.852252807309979</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.972113812232298</v>
+        <v>-4.946249757702041</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8378684177933422</v>
+        <v>0.8733964799154155</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.9586663108477141</v>
+        <v>-0.91945597485287</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.251870580491381</v>
+        <v>2.300579222398258</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273185</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.82762224003311</v>
+        <v>2.852804680343081</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.848986105238215</v>
+        <v>-4.823122050707958</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8876713736240771</v>
+        <v>0.9231994357461502</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.9586663108477141</v>
+        <v>-0.91945597485287</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.252422453524482</v>
+        <v>2.301131095431359</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.756894931924476</v>
+        <v>2.782077372234447</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.756175623787355</v>
+        <v>-4.730311569257099</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8540682580957866</v>
+        <v>0.8895963202178598</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.8658558293968548</v>
+        <v>-0.8266454934020107</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.237381434286363</v>
+        <v>2.28609007619324</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030422</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.758768407849077</v>
+        <v>2.783950848159047</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.707612571566325</v>
+        <v>-4.681748517036069</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8753669549087992</v>
+        <v>0.9108950170308725</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.8172927771758246</v>
+        <v>-0.7780824411809805</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.268392741543582</v>
+        <v>2.317101383450459</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942733</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.7538441163608</v>
+        <v>2.77902655667077</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.594941353330075</v>
+        <v>-4.569077298799819</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9155111507150224</v>
+        <v>0.9510392128370957</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.7046215589395743</v>
+        <v>-0.6654112229447302</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.331071180997055</v>
+        <v>2.379779822903933</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.551663147698817</v>
+        <v>3.734453264796405</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.759335412191467</v>
+        <v>2.788718188984113</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.529179791827533</v>
+        <v>-4.544837820126628</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9473070711467062</v>
+        <v>0.9704266366197141</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.7046215589395743</v>
+        <v>-0.6624726130856611</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.336562476827722</v>
+        <v>2.391234621132716</v>
       </c>
     </row>
   </sheetData>
